--- a/research/traditional_assets/database/data/tunisia/tunisia_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_rubber_tires.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvmt_stip" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,23 +589,26 @@
           <t>Rubber&amp; Tires</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.201</v>
+      </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1606132075471698</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.1606132075471698</v>
       </c>
       <c r="I2">
-        <v>-0.1004926108374384</v>
+        <v>0.1438679245283019</v>
       </c>
       <c r="J2">
-        <v>-0.1004926108374384</v>
+        <v>0.1411651548843046</v>
       </c>
       <c r="K2">
-        <v>-2.38</v>
+        <v>8.41</v>
       </c>
       <c r="L2">
-        <v>-0.1172413793103448</v>
+        <v>0.1983490566037736</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,64 +626,58 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.2465564738292011</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.9387183147969813</v>
+        <v>0.2150796040691755</v>
       </c>
       <c r="AB2">
-        <v>0.1793340310662028</v>
+        <v>0.2150796040691755</v>
       </c>
       <c r="AD2">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>26.305</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.8822575413558222</v>
-      </c>
-      <c r="AI2">
-        <v>-9.714285714285712</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.8787372640721564</v>
-      </c>
-      <c r="AK2">
-        <v>-7.119079837618402</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.65</v>
+        <v>2.59</v>
       </c>
       <c r="AM2">
-        <v>1.637</v>
+        <v>2.58</v>
       </c>
       <c r="AN2">
-        <v>-20.76335877862595</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-1.236363636363637</v>
+        <v>2.355212355212355</v>
       </c>
       <c r="AP2">
-        <v>-20.08015267175572</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-1.246182040317654</v>
+        <v>2.364341085271318</v>
       </c>
     </row>
     <row r="3">
@@ -697,23 +696,26 @@
           <t>Rubber&amp; Tires</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.201</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1606132075471698</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1606132075471698</v>
       </c>
       <c r="I3">
-        <v>-0.1004926108374384</v>
+        <v>0.1438679245283019</v>
       </c>
       <c r="J3">
-        <v>-0.1004926108374384</v>
+        <v>0.1411651548843046</v>
       </c>
       <c r="K3">
-        <v>-2.38</v>
+        <v>8.41</v>
       </c>
       <c r="L3">
-        <v>-0.1172413793103448</v>
+        <v>0.1983490566037736</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +724,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,64 +733,8767 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.2465564738292011</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.9387183147969813</v>
+        <v>0.2150796040691755</v>
       </c>
       <c r="AB3">
-        <v>0.1793340310662028</v>
+        <v>0.2150796040691755</v>
       </c>
       <c r="AD3">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>26.305</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.8822575413558222</v>
-      </c>
-      <c r="AI3">
-        <v>-9.714285714285712</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.8787372640721564</v>
-      </c>
-      <c r="AK3">
-        <v>-7.119079837618402</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.65</v>
+        <v>2.59</v>
       </c>
       <c r="AM3">
-        <v>1.637</v>
+        <v>2.58</v>
       </c>
       <c r="AN3">
-        <v>-20.76335877862595</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1.236363636363637</v>
+        <v>2.355212355212355</v>
       </c>
       <c r="AP3">
-        <v>-20.08015267175572</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-1.246182040317654</v>
+        <v>2.364341085271318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Société Tunisienne des Industries de Pneumatiques SA (BVMT:STIP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVMT:STIP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rubber&amp; Tires</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.99</v>
+      </c>
+      <c r="G2">
+        <v>5.39</v>
+      </c>
+      <c r="H2">
+        <v>0.308671327177188</v>
+      </c>
+      <c r="I2">
+        <v>5.39</v>
+      </c>
+      <c r="J2">
+        <v>5.64477132717719</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>5.3361</v>
+      </c>
+      <c r="M2">
+        <v>0.215079604069176</v>
+      </c>
+      <c r="N2">
+        <v>0.188946632864903</v>
+      </c>
+      <c r="O2">
+        <v>0.127966720183486</v>
+      </c>
+      <c r="P2">
+        <v>0.038845</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.215079604069176</v>
+      </c>
+      <c r="T2">
+        <v>15.0490082864903</v>
+      </c>
+      <c r="U2">
+        <v>0.934843411101598</v>
+      </c>
+      <c r="V2">
+        <v>79.60191645530099</v>
+      </c>
+      <c r="W2">
+        <v>24.42797350296852</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>5.39</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1505490825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.81</v>
+      </c>
+      <c r="AH2">
+        <v>0.853</v>
+      </c>
+      <c r="AI2">
+        <v>1.01</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>2.59</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2150796040691755</v>
+      </c>
+      <c r="C2">
+        <v>5.39</v>
+      </c>
+      <c r="D2">
+        <v>5.39</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>5.39</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.81</v>
+      </c>
+      <c r="K2">
+        <v>0.853</v>
+      </c>
+      <c r="L2">
+        <v>5.957</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.957</v>
+      </c>
+      <c r="O2">
+        <v>0.8935500000000001</v>
+      </c>
+      <c r="P2">
+        <v>5.06345</v>
+      </c>
+      <c r="Q2">
+        <v>5.916449999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2150796040691755</v>
+      </c>
+      <c r="T2">
+        <v>0.9348434111015981</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2148156346630718</v>
+      </c>
+      <c r="C3">
+        <v>5.338558418450567</v>
+      </c>
+      <c r="D3">
+        <v>5.392458418450566</v>
+      </c>
+      <c r="E3">
+        <v>0.0539</v>
+      </c>
+      <c r="F3">
+        <v>0.0539</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>5.39</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.81</v>
+      </c>
+      <c r="K3">
+        <v>0.853</v>
+      </c>
+      <c r="L3">
+        <v>5.957</v>
+      </c>
+      <c r="M3">
+        <v>0.00246323</v>
+      </c>
+      <c r="N3">
+        <v>5.95453677</v>
+      </c>
+      <c r="O3">
+        <v>0.8931805155000001</v>
+      </c>
+      <c r="P3">
+        <v>5.0613562545</v>
+      </c>
+      <c r="Q3">
+        <v>5.914356254499999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2165931158212846</v>
+      </c>
+      <c r="T3">
+        <v>0.9428698444292379</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>2418.369376793884</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.214551665256968</v>
+      </c>
+      <c r="C4">
+        <v>5.287119080529767</v>
+      </c>
+      <c r="D4">
+        <v>5.394919080529768</v>
+      </c>
+      <c r="E4">
+        <v>0.1078</v>
+      </c>
+      <c r="F4">
+        <v>0.1078</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>5.39</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.81</v>
+      </c>
+      <c r="K4">
+        <v>0.853</v>
+      </c>
+      <c r="L4">
+        <v>5.957</v>
+      </c>
+      <c r="M4">
+        <v>0.004926460000000001</v>
+      </c>
+      <c r="N4">
+        <v>5.95207354</v>
+      </c>
+      <c r="O4">
+        <v>0.8928110310000001</v>
+      </c>
+      <c r="P4">
+        <v>5.059262509</v>
+      </c>
+      <c r="Q4">
+        <v>5.912262509</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2181375155683347</v>
+      </c>
+      <c r="T4">
+        <v>0.9510600825186667</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>1209.184688396942</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2142876958508642</v>
+      </c>
+      <c r="C5">
+        <v>5.23568198931041</v>
+      </c>
+      <c r="D5">
+        <v>5.39738198931041</v>
+      </c>
+      <c r="E5">
+        <v>0.1617</v>
+      </c>
+      <c r="F5">
+        <v>0.1617</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>5.39</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.81</v>
+      </c>
+      <c r="K5">
+        <v>0.853</v>
+      </c>
+      <c r="L5">
+        <v>5.957</v>
+      </c>
+      <c r="M5">
+        <v>0.00738969</v>
+      </c>
+      <c r="N5">
+        <v>5.94961031</v>
+      </c>
+      <c r="O5">
+        <v>0.8924415465000001</v>
+      </c>
+      <c r="P5">
+        <v>5.0571687635</v>
+      </c>
+      <c r="Q5">
+        <v>5.9101687635</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2197137586091384</v>
+      </c>
+      <c r="T5">
+        <v>0.9594191914965369</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>806.1231255979615</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2140237264447605</v>
+      </c>
+      <c r="C6">
+        <v>5.18424714787092</v>
+      </c>
+      <c r="D6">
+        <v>5.39984714787092</v>
+      </c>
+      <c r="E6">
+        <v>0.2156</v>
+      </c>
+      <c r="F6">
+        <v>0.2156</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>5.39</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.81</v>
+      </c>
+      <c r="K6">
+        <v>0.853</v>
+      </c>
+      <c r="L6">
+        <v>5.957</v>
+      </c>
+      <c r="M6">
+        <v>0.009852920000000001</v>
+      </c>
+      <c r="N6">
+        <v>5.94714708</v>
+      </c>
+      <c r="O6">
+        <v>0.8920720620000001</v>
+      </c>
+      <c r="P6">
+        <v>5.055075017999999</v>
+      </c>
+      <c r="Q6">
+        <v>5.908075017999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2213228400466255</v>
+      </c>
+      <c r="T6">
+        <v>0.967952448578113</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>604.592344198471</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2137597570386567</v>
+      </c>
+      <c r="C7">
+        <v>5.132814559295346</v>
+      </c>
+      <c r="D7">
+        <v>5.402314559295346</v>
+      </c>
+      <c r="E7">
+        <v>0.2695</v>
+      </c>
+      <c r="F7">
+        <v>0.2695</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>5.39</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.81</v>
+      </c>
+      <c r="K7">
+        <v>0.853</v>
+      </c>
+      <c r="L7">
+        <v>5.957</v>
+      </c>
+      <c r="M7">
+        <v>0.01231615</v>
+      </c>
+      <c r="N7">
+        <v>5.94468385</v>
+      </c>
+      <c r="O7">
+        <v>0.8917025775</v>
+      </c>
+      <c r="P7">
+        <v>5.052981272499999</v>
+      </c>
+      <c r="Q7">
+        <v>5.905981272499999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2229657968827966</v>
+      </c>
+      <c r="T7">
+        <v>0.9766653531771959</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>483.6738753587768</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2134957876325529</v>
+      </c>
+      <c r="C8">
+        <v>5.081384226673374</v>
+      </c>
+      <c r="D8">
+        <v>5.404784226673375</v>
+      </c>
+      <c r="E8">
+        <v>0.3234</v>
+      </c>
+      <c r="F8">
+        <v>0.3234</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>5.39</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.81</v>
+      </c>
+      <c r="K8">
+        <v>0.853</v>
+      </c>
+      <c r="L8">
+        <v>5.957</v>
+      </c>
+      <c r="M8">
+        <v>0.01477938</v>
+      </c>
+      <c r="N8">
+        <v>5.94222062</v>
+      </c>
+      <c r="O8">
+        <v>0.8913330930000001</v>
+      </c>
+      <c r="P8">
+        <v>5.050887527</v>
+      </c>
+      <c r="Q8">
+        <v>5.903887526999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2246437102473968</v>
+      </c>
+      <c r="T8">
+        <v>0.9855636387251954</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>403.0615627989807</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2132318182264492</v>
+      </c>
+      <c r="C9">
+        <v>5.029956153100352</v>
+      </c>
+      <c r="D9">
+        <v>5.407256153100352</v>
+      </c>
+      <c r="E9">
+        <v>0.3773</v>
+      </c>
+      <c r="F9">
+        <v>0.3773</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>5.39</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.81</v>
+      </c>
+      <c r="K9">
+        <v>0.853</v>
+      </c>
+      <c r="L9">
+        <v>5.957</v>
+      </c>
+      <c r="M9">
+        <v>0.01724261</v>
+      </c>
+      <c r="N9">
+        <v>5.93975739</v>
+      </c>
+      <c r="O9">
+        <v>0.8909636085000001</v>
+      </c>
+      <c r="P9">
+        <v>5.0487937815</v>
+      </c>
+      <c r="Q9">
+        <v>5.901793781499999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2263577077703755</v>
+      </c>
+      <c r="T9">
+        <v>0.9946532852527218</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>345.4813395419834</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2129678488203454</v>
+      </c>
+      <c r="C10">
+        <v>4.978530341677283</v>
+      </c>
+      <c r="D10">
+        <v>5.409730341677283</v>
+      </c>
+      <c r="E10">
+        <v>0.4312</v>
+      </c>
+      <c r="F10">
+        <v>0.4312</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5.39</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.81</v>
+      </c>
+      <c r="K10">
+        <v>0.853</v>
+      </c>
+      <c r="L10">
+        <v>5.957</v>
+      </c>
+      <c r="M10">
+        <v>0.01970584</v>
+      </c>
+      <c r="N10">
+        <v>5.93729416</v>
+      </c>
+      <c r="O10">
+        <v>0.890594124</v>
+      </c>
+      <c r="P10">
+        <v>5.046700036</v>
+      </c>
+      <c r="Q10">
+        <v>5.899700036</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2281089661090711</v>
+      </c>
+      <c r="T10">
+        <v>1.003940532791716</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>302.2961720992355</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2127038794142417</v>
+      </c>
+      <c r="C11">
+        <v>4.927106795510854</v>
+      </c>
+      <c r="D11">
+        <v>5.412206795510854</v>
+      </c>
+      <c r="E11">
+        <v>0.4851</v>
+      </c>
+      <c r="F11">
+        <v>0.4851</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>5.39</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.81</v>
+      </c>
+      <c r="K11">
+        <v>0.853</v>
+      </c>
+      <c r="L11">
+        <v>5.957</v>
+      </c>
+      <c r="M11">
+        <v>0.02216907</v>
+      </c>
+      <c r="N11">
+        <v>5.93483093</v>
+      </c>
+      <c r="O11">
+        <v>0.8902246395000001</v>
+      </c>
+      <c r="P11">
+        <v>5.044606290499999</v>
+      </c>
+      <c r="Q11">
+        <v>5.897606290499999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2298987136420238</v>
+      </c>
+      <c r="T11">
+        <v>1.013431895661238</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>268.7077085326538</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2124399100081379</v>
+      </c>
+      <c r="C12">
+        <v>4.87568551771344</v>
+      </c>
+      <c r="D12">
+        <v>5.41468551771344</v>
+      </c>
+      <c r="E12">
+        <v>0.539</v>
+      </c>
+      <c r="F12">
+        <v>0.539</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>5.39</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.81</v>
+      </c>
+      <c r="K12">
+        <v>0.853</v>
+      </c>
+      <c r="L12">
+        <v>5.957</v>
+      </c>
+      <c r="M12">
+        <v>0.0246323</v>
+      </c>
+      <c r="N12">
+        <v>5.932367699999999</v>
+      </c>
+      <c r="O12">
+        <v>0.889855155</v>
+      </c>
+      <c r="P12">
+        <v>5.042512544999999</v>
+      </c>
+      <c r="Q12">
+        <v>5.895512544999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2317282333423755</v>
+      </c>
+      <c r="T12">
+        <v>1.023134177705638</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>241.8369376793884</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2121759406020342</v>
+      </c>
+      <c r="C13">
+        <v>4.824266511403121</v>
+      </c>
+      <c r="D13">
+        <v>5.417166511403122</v>
+      </c>
+      <c r="E13">
+        <v>0.5929</v>
+      </c>
+      <c r="F13">
+        <v>0.5929</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>5.39</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.81</v>
+      </c>
+      <c r="K13">
+        <v>0.853</v>
+      </c>
+      <c r="L13">
+        <v>5.957</v>
+      </c>
+      <c r="M13">
+        <v>0.02709553</v>
+      </c>
+      <c r="N13">
+        <v>5.929904469999999</v>
+      </c>
+      <c r="O13">
+        <v>0.8894856705</v>
+      </c>
+      <c r="P13">
+        <v>5.040418799499999</v>
+      </c>
+      <c r="Q13">
+        <v>5.893418799499999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2335988658449822</v>
+      </c>
+      <c r="T13">
+        <v>1.033054488560024</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>219.8517615267167</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2119119711959304</v>
+      </c>
+      <c r="C14">
+        <v>4.772849779703699</v>
+      </c>
+      <c r="D14">
+        <v>5.419649779703699</v>
+      </c>
+      <c r="E14">
+        <v>0.6467999999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.6467999999999999</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>5.39</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.81</v>
+      </c>
+      <c r="K14">
+        <v>0.853</v>
+      </c>
+      <c r="L14">
+        <v>5.957</v>
+      </c>
+      <c r="M14">
+        <v>0.02955876</v>
+      </c>
+      <c r="N14">
+        <v>5.92744124</v>
+      </c>
+      <c r="O14">
+        <v>0.8891161860000002</v>
+      </c>
+      <c r="P14">
+        <v>5.038325054</v>
+      </c>
+      <c r="Q14">
+        <v>5.891325054</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2355120127226482</v>
+      </c>
+      <c r="T14">
+        <v>1.043200261024738</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>201.5307813994904</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2116480017898266</v>
+      </c>
+      <c r="C15">
+        <v>4.721435325744701</v>
+      </c>
+      <c r="D15">
+        <v>5.422135325744701</v>
+      </c>
+      <c r="E15">
+        <v>0.7007</v>
+      </c>
+      <c r="F15">
+        <v>0.7007</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>5.39</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.81</v>
+      </c>
+      <c r="K15">
+        <v>0.853</v>
+      </c>
+      <c r="L15">
+        <v>5.957</v>
+      </c>
+      <c r="M15">
+        <v>0.03202199</v>
+      </c>
+      <c r="N15">
+        <v>5.92497801</v>
+      </c>
+      <c r="O15">
+        <v>0.8887467015000001</v>
+      </c>
+      <c r="P15">
+        <v>5.0362313085</v>
+      </c>
+      <c r="Q15">
+        <v>5.889231308499999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2374691399883064</v>
+      </c>
+      <c r="T15">
+        <v>1.053579269638065</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>186.0284135995296</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2113840323837228</v>
+      </c>
+      <c r="C16">
+        <v>4.670023152661399</v>
+      </c>
+      <c r="D16">
+        <v>5.424623152661399</v>
+      </c>
+      <c r="E16">
+        <v>0.7546</v>
+      </c>
+      <c r="F16">
+        <v>0.7546</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>5.39</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.81</v>
+      </c>
+      <c r="K16">
+        <v>0.853</v>
+      </c>
+      <c r="L16">
+        <v>5.957</v>
+      </c>
+      <c r="M16">
+        <v>0.03448522</v>
+      </c>
+      <c r="N16">
+        <v>5.92251478</v>
+      </c>
+      <c r="O16">
+        <v>0.8883772170000002</v>
+      </c>
+      <c r="P16">
+        <v>5.034137563</v>
+      </c>
+      <c r="Q16">
+        <v>5.887137563</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2394717818415382</v>
+      </c>
+      <c r="T16">
+        <v>1.064199650544726</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.038845</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>172.7406697709917</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.211120062977619</v>
+      </c>
+      <c r="C17">
+        <v>4.618613263594823</v>
+      </c>
+      <c r="D17">
+        <v>5.427113263594823</v>
+      </c>
+      <c r="E17">
+        <v>0.8084999999999999</v>
+      </c>
+      <c r="F17">
+        <v>0.8084999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>5.39</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.81</v>
+      </c>
+      <c r="K17">
+        <v>0.853</v>
+      </c>
+      <c r="L17">
+        <v>5.957</v>
+      </c>
+      <c r="M17">
+        <v>0.03694845</v>
+      </c>
+      <c r="N17">
+        <v>5.92005155</v>
+      </c>
+      <c r="O17">
+        <v>0.8880077325000002</v>
+      </c>
+      <c r="P17">
+        <v>5.0320438175</v>
+      </c>
+      <c r="Q17">
+        <v>5.8850438175</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2415215446795518</v>
+      </c>
+      <c r="T17">
+        <v>1.075069922766838</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.038845</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>161.2246251195923</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2108560935715154</v>
+      </c>
+      <c r="C18">
+        <v>4.567205661691771</v>
+      </c>
+      <c r="D18">
+        <v>5.429605661691771</v>
+      </c>
+      <c r="E18">
+        <v>0.8623999999999999</v>
+      </c>
+      <c r="F18">
+        <v>0.8623999999999999</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>5.39</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.81</v>
+      </c>
+      <c r="K18">
+        <v>0.853</v>
+      </c>
+      <c r="L18">
+        <v>5.957</v>
+      </c>
+      <c r="M18">
+        <v>0.03941168</v>
+      </c>
+      <c r="N18">
+        <v>5.91758832</v>
+      </c>
+      <c r="O18">
+        <v>0.8876382480000001</v>
+      </c>
+      <c r="P18">
+        <v>5.029950072</v>
+      </c>
+      <c r="Q18">
+        <v>5.882950072</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2436201113946611</v>
+      </c>
+      <c r="T18">
+        <v>1.086199010994238</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.038845</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>151.1480860496178</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2105921241654115</v>
+      </c>
+      <c r="C19">
+        <v>4.515800350104828</v>
+      </c>
+      <c r="D19">
+        <v>5.432100350104828</v>
+      </c>
+      <c r="E19">
+        <v>0.9163</v>
+      </c>
+      <c r="F19">
+        <v>0.9163</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>5.39</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.81</v>
+      </c>
+      <c r="K19">
+        <v>0.853</v>
+      </c>
+      <c r="L19">
+        <v>5.957</v>
+      </c>
+      <c r="M19">
+        <v>0.04187491</v>
+      </c>
+      <c r="N19">
+        <v>5.91512509</v>
+      </c>
+      <c r="O19">
+        <v>0.8872687635000002</v>
+      </c>
+      <c r="P19">
+        <v>5.0278563265</v>
+      </c>
+      <c r="Q19">
+        <v>5.8808563265</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2457692459824236</v>
+      </c>
+      <c r="T19">
+        <v>1.097596270022298</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.038845</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>142.2570221643462</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2103281547593078</v>
+      </c>
+      <c r="C20">
+        <v>4.464397331992372</v>
+      </c>
+      <c r="D20">
+        <v>5.434597331992372</v>
+      </c>
+      <c r="E20">
+        <v>0.9702</v>
+      </c>
+      <c r="F20">
+        <v>0.9702</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>5.39</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.81</v>
+      </c>
+      <c r="K20">
+        <v>0.853</v>
+      </c>
+      <c r="L20">
+        <v>5.957</v>
+      </c>
+      <c r="M20">
+        <v>0.04433814000000001</v>
+      </c>
+      <c r="N20">
+        <v>5.91266186</v>
+      </c>
+      <c r="O20">
+        <v>0.8868992790000001</v>
+      </c>
+      <c r="P20">
+        <v>5.025762581</v>
+      </c>
+      <c r="Q20">
+        <v>5.878762581</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2479707984869607</v>
+      </c>
+      <c r="T20">
+        <v>1.109271510977872</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.038845</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>134.3538542663269</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2100641853532041</v>
+      </c>
+      <c r="C21">
+        <v>4.412996610518593</v>
+      </c>
+      <c r="D21">
+        <v>5.437096610518592</v>
+      </c>
+      <c r="E21">
+        <v>1.0241</v>
+      </c>
+      <c r="F21">
+        <v>1.0241</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>5.39</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.81</v>
+      </c>
+      <c r="K21">
+        <v>0.853</v>
+      </c>
+      <c r="L21">
+        <v>5.957</v>
+      </c>
+      <c r="M21">
+        <v>0.04680137</v>
+      </c>
+      <c r="N21">
+        <v>5.91019863</v>
+      </c>
+      <c r="O21">
+        <v>0.8865297945000001</v>
+      </c>
+      <c r="P21">
+        <v>5.0236688355</v>
+      </c>
+      <c r="Q21">
+        <v>5.876668835499999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2502267103125976</v>
+      </c>
+      <c r="T21">
+        <v>1.121235029487904</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.038845</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>127.2825987786255</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2098002159471003</v>
+      </c>
+      <c r="C22">
+        <v>4.361598188853502</v>
+      </c>
+      <c r="D22">
+        <v>5.439598188853502</v>
+      </c>
+      <c r="E22">
+        <v>1.078</v>
+      </c>
+      <c r="F22">
+        <v>1.078</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>5.39</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.81</v>
+      </c>
+      <c r="K22">
+        <v>0.853</v>
+      </c>
+      <c r="L22">
+        <v>5.957</v>
+      </c>
+      <c r="M22">
+        <v>0.04926460000000001</v>
+      </c>
+      <c r="N22">
+        <v>5.9077354</v>
+      </c>
+      <c r="O22">
+        <v>0.8861603100000002</v>
+      </c>
+      <c r="P22">
+        <v>5.02157509</v>
+      </c>
+      <c r="Q22">
+        <v>5.87457509</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2525390199338753</v>
+      </c>
+      <c r="T22">
+        <v>1.133497635960688</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.038845</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>120.9184688396942</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2095362465409965</v>
+      </c>
+      <c r="C23">
+        <v>4.31020207017295</v>
+      </c>
+      <c r="D23">
+        <v>5.442102070172949</v>
+      </c>
+      <c r="E23">
+        <v>1.1319</v>
+      </c>
+      <c r="F23">
+        <v>1.1319</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>5.39</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.81</v>
+      </c>
+      <c r="K23">
+        <v>0.853</v>
+      </c>
+      <c r="L23">
+        <v>5.957</v>
+      </c>
+      <c r="M23">
+        <v>0.05172783</v>
+      </c>
+      <c r="N23">
+        <v>5.90527217</v>
+      </c>
+      <c r="O23">
+        <v>0.8857908255000001</v>
+      </c>
+      <c r="P23">
+        <v>5.0194813445</v>
+      </c>
+      <c r="Q23">
+        <v>5.8724813445</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2549098690392361</v>
+      </c>
+      <c r="T23">
+        <v>1.146070688166959</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.038845</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>115.1604465139945</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2092722771348928</v>
+      </c>
+      <c r="C24">
+        <v>4.258808257658634</v>
+      </c>
+      <c r="D24">
+        <v>5.444608257658635</v>
+      </c>
+      <c r="E24">
+        <v>1.1858</v>
+      </c>
+      <c r="F24">
+        <v>1.1858</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>5.39</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.81</v>
+      </c>
+      <c r="K24">
+        <v>0.853</v>
+      </c>
+      <c r="L24">
+        <v>5.957</v>
+      </c>
+      <c r="M24">
+        <v>0.05419106000000001</v>
+      </c>
+      <c r="N24">
+        <v>5.90280894</v>
+      </c>
+      <c r="O24">
+        <v>0.8854213410000001</v>
+      </c>
+      <c r="P24">
+        <v>5.017387599</v>
+      </c>
+      <c r="Q24">
+        <v>5.870387599</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2573415091472984</v>
+      </c>
+      <c r="T24">
+        <v>1.158966126327238</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.038845</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>109.9258807633584</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.209008307728789</v>
+      </c>
+      <c r="C25">
+        <v>4.207416754498121</v>
+      </c>
+      <c r="D25">
+        <v>5.447116754498121</v>
+      </c>
+      <c r="E25">
+        <v>1.2397</v>
+      </c>
+      <c r="F25">
+        <v>1.2397</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>5.39</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.81</v>
+      </c>
+      <c r="K25">
+        <v>0.853</v>
+      </c>
+      <c r="L25">
+        <v>5.957</v>
+      </c>
+      <c r="M25">
+        <v>0.05665429000000001</v>
+      </c>
+      <c r="N25">
+        <v>5.90034571</v>
+      </c>
+      <c r="O25">
+        <v>0.8850518565000001</v>
+      </c>
+      <c r="P25">
+        <v>5.015293853499999</v>
+      </c>
+      <c r="Q25">
+        <v>5.868293853499999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.259836308738687</v>
+      </c>
+      <c r="T25">
+        <v>1.172196510933238</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.038845</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>105.1464946432123</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2087443383226852</v>
+      </c>
+      <c r="C26">
+        <v>4.156027563884849</v>
+      </c>
+      <c r="D26">
+        <v>5.449627563884849</v>
+      </c>
+      <c r="E26">
+        <v>1.2936</v>
+      </c>
+      <c r="F26">
+        <v>1.2936</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>5.39</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.81</v>
+      </c>
+      <c r="K26">
+        <v>0.853</v>
+      </c>
+      <c r="L26">
+        <v>5.957</v>
+      </c>
+      <c r="M26">
+        <v>0.05911752</v>
+      </c>
+      <c r="N26">
+        <v>5.89788248</v>
+      </c>
+      <c r="O26">
+        <v>0.8846823720000001</v>
+      </c>
+      <c r="P26">
+        <v>5.013200107999999</v>
+      </c>
+      <c r="Q26">
+        <v>5.866200107999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2623967609509016</v>
+      </c>
+      <c r="T26">
+        <v>1.185775063555185</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.038845</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>100.7653906997452</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2084803689165814</v>
+      </c>
+      <c r="C27">
+        <v>4.104640689018149</v>
+      </c>
+      <c r="D27">
+        <v>5.452140689018149</v>
+      </c>
+      <c r="E27">
+        <v>1.3475</v>
+      </c>
+      <c r="F27">
+        <v>1.3475</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>5.39</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.81</v>
+      </c>
+      <c r="K27">
+        <v>0.853</v>
+      </c>
+      <c r="L27">
+        <v>5.957</v>
+      </c>
+      <c r="M27">
+        <v>0.06158075</v>
+      </c>
+      <c r="N27">
+        <v>5.89541925</v>
+      </c>
+      <c r="O27">
+        <v>0.8843128875000001</v>
+      </c>
+      <c r="P27">
+        <v>5.0111063625</v>
+      </c>
+      <c r="Q27">
+        <v>5.864106362499999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2650254918887752</v>
+      </c>
+      <c r="T27">
+        <v>1.199715710913717</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.038845</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>96.73477507175537</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2082163995104777</v>
+      </c>
+      <c r="C28">
+        <v>4.053256133103256</v>
+      </c>
+      <c r="D28">
+        <v>5.454656133103255</v>
+      </c>
+      <c r="E28">
+        <v>1.4014</v>
+      </c>
+      <c r="F28">
+        <v>1.4014</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>5.39</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.81</v>
+      </c>
+      <c r="K28">
+        <v>0.853</v>
+      </c>
+      <c r="L28">
+        <v>5.957</v>
+      </c>
+      <c r="M28">
+        <v>0.06404398</v>
+      </c>
+      <c r="N28">
+        <v>5.89295602</v>
+      </c>
+      <c r="O28">
+        <v>0.8839434030000001</v>
+      </c>
+      <c r="P28">
+        <v>5.009012617</v>
+      </c>
+      <c r="Q28">
+        <v>5.862012617</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2677252696087536</v>
+      </c>
+      <c r="T28">
+        <v>1.214033132525183</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.038845</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>93.01420679976478</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2079524301043739</v>
+      </c>
+      <c r="C29">
+        <v>4.001873899351322</v>
+      </c>
+      <c r="D29">
+        <v>5.457173899351322</v>
+      </c>
+      <c r="E29">
+        <v>1.4553</v>
+      </c>
+      <c r="F29">
+        <v>1.4553</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>5.39</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.81</v>
+      </c>
+      <c r="K29">
+        <v>0.853</v>
+      </c>
+      <c r="L29">
+        <v>5.957</v>
+      </c>
+      <c r="M29">
+        <v>0.06650721000000001</v>
+      </c>
+      <c r="N29">
+        <v>5.89049279</v>
+      </c>
+      <c r="O29">
+        <v>0.8835739185000001</v>
+      </c>
+      <c r="P29">
+        <v>5.0069188715</v>
+      </c>
+      <c r="Q29">
+        <v>5.8599188715</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2704990138416081</v>
+      </c>
+      <c r="T29">
+        <v>1.228742812262991</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.038845</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>89.56923617755126</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2076884606982702</v>
+      </c>
+      <c r="C30">
+        <v>3.950493990979433</v>
+      </c>
+      <c r="D30">
+        <v>5.459693990979433</v>
+      </c>
+      <c r="E30">
+        <v>1.5092</v>
+      </c>
+      <c r="F30">
+        <v>1.5092</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>5.39</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.81</v>
+      </c>
+      <c r="K30">
+        <v>0.853</v>
+      </c>
+      <c r="L30">
+        <v>5.957</v>
+      </c>
+      <c r="M30">
+        <v>0.06897044000000001</v>
+      </c>
+      <c r="N30">
+        <v>5.88802956</v>
+      </c>
+      <c r="O30">
+        <v>0.883204434</v>
+      </c>
+      <c r="P30">
+        <v>5.004825126</v>
+      </c>
+      <c r="Q30">
+        <v>5.857825126</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2733498065253752</v>
+      </c>
+      <c r="T30">
+        <v>1.243861094215738</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.038845</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>86.37033488549586</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2074244912921664</v>
+      </c>
+      <c r="C31">
+        <v>3.89911641121062</v>
+      </c>
+      <c r="D31">
+        <v>5.46221641121062</v>
+      </c>
+      <c r="E31">
+        <v>1.5631</v>
+      </c>
+      <c r="F31">
+        <v>1.5631</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>5.39</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.81</v>
+      </c>
+      <c r="K31">
+        <v>0.853</v>
+      </c>
+      <c r="L31">
+        <v>5.957</v>
+      </c>
+      <c r="M31">
+        <v>0.07143366999999999</v>
+      </c>
+      <c r="N31">
+        <v>5.88556633</v>
+      </c>
+      <c r="O31">
+        <v>0.8828349495000001</v>
+      </c>
+      <c r="P31">
+        <v>5.002731380499999</v>
+      </c>
+      <c r="Q31">
+        <v>5.855731380499999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2762809032284034</v>
+      </c>
+      <c r="T31">
+        <v>1.259405243265745</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.038845</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>83.3920474756512</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2071605218860626</v>
+      </c>
+      <c r="C32">
+        <v>3.84774116327387</v>
+      </c>
+      <c r="D32">
+        <v>5.46474116327387</v>
+      </c>
+      <c r="E32">
+        <v>1.617</v>
+      </c>
+      <c r="F32">
+        <v>1.617</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>5.39</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.81</v>
+      </c>
+      <c r="K32">
+        <v>0.853</v>
+      </c>
+      <c r="L32">
+        <v>5.957</v>
+      </c>
+      <c r="M32">
+        <v>0.0738969</v>
+      </c>
+      <c r="N32">
+        <v>5.8831031</v>
+      </c>
+      <c r="O32">
+        <v>0.8824654650000001</v>
+      </c>
+      <c r="P32">
+        <v>5.000637634999999</v>
+      </c>
+      <c r="Q32">
+        <v>5.853637634999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.279295745551518</v>
+      </c>
+      <c r="T32">
+        <v>1.275393510860037</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.038845</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>80.61231255979614</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2068965524799588</v>
+      </c>
+      <c r="C33">
+        <v>3.796368250404146</v>
+      </c>
+      <c r="D33">
+        <v>5.467268250404146</v>
+      </c>
+      <c r="E33">
+        <v>1.6709</v>
+      </c>
+      <c r="F33">
+        <v>1.6709</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>5.39</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.81</v>
+      </c>
+      <c r="K33">
+        <v>0.853</v>
+      </c>
+      <c r="L33">
+        <v>5.957</v>
+      </c>
+      <c r="M33">
+        <v>0.07636013</v>
+      </c>
+      <c r="N33">
+        <v>5.88063987</v>
+      </c>
+      <c r="O33">
+        <v>0.8820959805</v>
+      </c>
+      <c r="P33">
+        <v>4.9985438895</v>
+      </c>
+      <c r="Q33">
+        <v>5.851543889499999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.282397974608636</v>
+      </c>
+      <c r="T33">
+        <v>1.291845206500542</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.038845</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>78.01191538044789</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2066325830738551</v>
+      </c>
+      <c r="C34">
+        <v>3.744997675842394</v>
+      </c>
+      <c r="D34">
+        <v>5.469797675842394</v>
+      </c>
+      <c r="E34">
+        <v>1.7248</v>
+      </c>
+      <c r="F34">
+        <v>1.7248</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>5.39</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.81</v>
+      </c>
+      <c r="K34">
+        <v>0.853</v>
+      </c>
+      <c r="L34">
+        <v>5.957</v>
+      </c>
+      <c r="M34">
+        <v>0.07882336000000001</v>
+      </c>
+      <c r="N34">
+        <v>5.87817664</v>
+      </c>
+      <c r="O34">
+        <v>0.8817264960000001</v>
+      </c>
+      <c r="P34">
+        <v>4.996450144</v>
+      </c>
+      <c r="Q34">
+        <v>5.849450144</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2855914456968457</v>
+      </c>
+      <c r="T34">
+        <v>1.308780775542237</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.038845</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>75.57404302480887</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2063686136677513</v>
+      </c>
+      <c r="C35">
+        <v>3.693629442835565</v>
+      </c>
+      <c r="D35">
+        <v>5.472329442835565</v>
+      </c>
+      <c r="E35">
+        <v>1.7787</v>
+      </c>
+      <c r="F35">
+        <v>1.7787</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>5.39</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.81</v>
+      </c>
+      <c r="K35">
+        <v>0.853</v>
+      </c>
+      <c r="L35">
+        <v>5.957</v>
+      </c>
+      <c r="M35">
+        <v>0.08128659000000001</v>
+      </c>
+      <c r="N35">
+        <v>5.875713409999999</v>
+      </c>
+      <c r="O35">
+        <v>0.8813570115</v>
+      </c>
+      <c r="P35">
+        <v>4.994356398499999</v>
+      </c>
+      <c r="Q35">
+        <v>5.847356398499999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2888802442802259</v>
+      </c>
+      <c r="T35">
+        <v>1.326221883958312</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.038845</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>73.28392050890558</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2061046442616476</v>
+      </c>
+      <c r="C36">
+        <v>3.642263554636622</v>
+      </c>
+      <c r="D36">
+        <v>5.474863554636622</v>
+      </c>
+      <c r="E36">
+        <v>1.8326</v>
+      </c>
+      <c r="F36">
+        <v>1.8326</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>5.39</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.81</v>
+      </c>
+      <c r="K36">
+        <v>0.853</v>
+      </c>
+      <c r="L36">
+        <v>5.957</v>
+      </c>
+      <c r="M36">
+        <v>0.08374982</v>
+      </c>
+      <c r="N36">
+        <v>5.873250179999999</v>
+      </c>
+      <c r="O36">
+        <v>0.880987527</v>
+      </c>
+      <c r="P36">
+        <v>4.992262652999999</v>
+      </c>
+      <c r="Q36">
+        <v>5.845262652999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2922687034267388</v>
+      </c>
+      <c r="T36">
+        <v>1.344191510811237</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.038845</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>71.12851108217306</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2058406748555438</v>
+      </c>
+      <c r="C37">
+        <v>3.590900014504555</v>
+      </c>
+      <c r="D37">
+        <v>5.477400014504555</v>
+      </c>
+      <c r="E37">
+        <v>1.8865</v>
+      </c>
+      <c r="F37">
+        <v>1.8865</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>5.39</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.81</v>
+      </c>
+      <c r="K37">
+        <v>0.853</v>
+      </c>
+      <c r="L37">
+        <v>5.957</v>
+      </c>
+      <c r="M37">
+        <v>0.08621305000000001</v>
+      </c>
+      <c r="N37">
+        <v>5.870786949999999</v>
+      </c>
+      <c r="O37">
+        <v>0.8806180425000001</v>
+      </c>
+      <c r="P37">
+        <v>4.990168907499999</v>
+      </c>
+      <c r="Q37">
+        <v>5.843168907499999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2957614228546828</v>
+      </c>
+      <c r="T37">
+        <v>1.362714049259637</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.038845</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>69.09626790839668</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2055767054494401</v>
+      </c>
+      <c r="C38">
+        <v>3.5395388257044</v>
+      </c>
+      <c r="D38">
+        <v>5.4799388257044</v>
+      </c>
+      <c r="E38">
+        <v>1.9404</v>
+      </c>
+      <c r="F38">
+        <v>1.9404</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>5.39</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.81</v>
+      </c>
+      <c r="K38">
+        <v>0.853</v>
+      </c>
+      <c r="L38">
+        <v>5.957</v>
+      </c>
+      <c r="M38">
+        <v>0.08867628000000001</v>
+      </c>
+      <c r="N38">
+        <v>5.86832372</v>
+      </c>
+      <c r="O38">
+        <v>0.8802485580000001</v>
+      </c>
+      <c r="P38">
+        <v>4.988075162</v>
+      </c>
+      <c r="Q38">
+        <v>5.841075162</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2993632897647501</v>
+      </c>
+      <c r="T38">
+        <v>1.38181541703455</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.038845</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>67.17692713316345</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2053127360433363</v>
+      </c>
+      <c r="C39">
+        <v>3.488179991507245</v>
+      </c>
+      <c r="D39">
+        <v>5.482479991507245</v>
+      </c>
+      <c r="E39">
+        <v>1.9943</v>
+      </c>
+      <c r="F39">
+        <v>1.9943</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>5.39</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.81</v>
+      </c>
+      <c r="K39">
+        <v>0.853</v>
+      </c>
+      <c r="L39">
+        <v>5.957</v>
+      </c>
+      <c r="M39">
+        <v>0.09113951000000001</v>
+      </c>
+      <c r="N39">
+        <v>5.86586049</v>
+      </c>
+      <c r="O39">
+        <v>0.8798790735000002</v>
+      </c>
+      <c r="P39">
+        <v>4.9859814165</v>
+      </c>
+      <c r="Q39">
+        <v>5.838981416499999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3030795016560894</v>
+      </c>
+      <c r="T39">
+        <v>1.401523177437237</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.038845</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>65.36133450794281</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2050487666372326</v>
+      </c>
+      <c r="C40">
+        <v>3.43682351519025</v>
+      </c>
+      <c r="D40">
+        <v>5.48502351519025</v>
+      </c>
+      <c r="E40">
+        <v>2.0482</v>
+      </c>
+      <c r="F40">
+        <v>2.0482</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>5.39</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.81</v>
+      </c>
+      <c r="K40">
+        <v>0.853</v>
+      </c>
+      <c r="L40">
+        <v>5.957</v>
+      </c>
+      <c r="M40">
+        <v>0.09360274</v>
+      </c>
+      <c r="N40">
+        <v>5.86339726</v>
+      </c>
+      <c r="O40">
+        <v>0.8795095890000002</v>
+      </c>
+      <c r="P40">
+        <v>4.983887671</v>
+      </c>
+      <c r="Q40">
+        <v>5.836887671</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3069155913503751</v>
+      </c>
+      <c r="T40">
+        <v>1.421866672046463</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.038845</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>63.64129938931275</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2047847972311288</v>
+      </c>
+      <c r="C41">
+        <v>3.385469400036661</v>
+      </c>
+      <c r="D41">
+        <v>5.487569400036661</v>
+      </c>
+      <c r="E41">
+        <v>2.1021</v>
+      </c>
+      <c r="F41">
+        <v>2.1021</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>5.39</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.81</v>
+      </c>
+      <c r="K41">
+        <v>0.853</v>
+      </c>
+      <c r="L41">
+        <v>5.957</v>
+      </c>
+      <c r="M41">
+        <v>0.09606597000000001</v>
+      </c>
+      <c r="N41">
+        <v>5.86093403</v>
+      </c>
+      <c r="O41">
+        <v>0.8791401045000001</v>
+      </c>
+      <c r="P41">
+        <v>4.9817939255</v>
+      </c>
+      <c r="Q41">
+        <v>5.8347939255</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3108774544772603</v>
+      </c>
+      <c r="T41">
+        <v>1.442877166478942</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.038845</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>62.00947119984318</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.204520827825025</v>
+      </c>
+      <c r="C42">
+        <v>3.334117649335822</v>
+      </c>
+      <c r="D42">
+        <v>5.490117649335822</v>
+      </c>
+      <c r="E42">
+        <v>2.156</v>
+      </c>
+      <c r="F42">
+        <v>2.156</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>5.39</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.81</v>
+      </c>
+      <c r="K42">
+        <v>0.853</v>
+      </c>
+      <c r="L42">
+        <v>5.957</v>
+      </c>
+      <c r="M42">
+        <v>0.09852920000000001</v>
+      </c>
+      <c r="N42">
+        <v>5.8584708</v>
+      </c>
+      <c r="O42">
+        <v>0.8787706200000002</v>
+      </c>
+      <c r="P42">
+        <v>4.97970018</v>
+      </c>
+      <c r="Q42">
+        <v>5.83270018</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.314971379708375</v>
+      </c>
+      <c r="T42">
+        <v>1.464588010725837</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.038845</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>60.45923441984711</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2042568584189212</v>
+      </c>
+      <c r="C43">
+        <v>3.282768266383186</v>
+      </c>
+      <c r="D43">
+        <v>5.492668266383186</v>
+      </c>
+      <c r="E43">
+        <v>2.2099</v>
+      </c>
+      <c r="F43">
+        <v>2.2099</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>5.39</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.81</v>
+      </c>
+      <c r="K43">
+        <v>0.853</v>
+      </c>
+      <c r="L43">
+        <v>5.957</v>
+      </c>
+      <c r="M43">
+        <v>0.10099243</v>
+      </c>
+      <c r="N43">
+        <v>5.85600757</v>
+      </c>
+      <c r="O43">
+        <v>0.8784011355000001</v>
+      </c>
+      <c r="P43">
+        <v>4.9776064345</v>
+      </c>
+      <c r="Q43">
+        <v>5.8306064345</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3192040820659682</v>
+      </c>
+      <c r="T43">
+        <v>1.487034815794661</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.038845</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>58.98461894619229</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2039928890128175</v>
+      </c>
+      <c r="C44">
+        <v>3.231421254480338</v>
+      </c>
+      <c r="D44">
+        <v>5.495221254480338</v>
+      </c>
+      <c r="E44">
+        <v>2.2638</v>
+      </c>
+      <c r="F44">
+        <v>2.2638</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>5.39</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.81</v>
+      </c>
+      <c r="K44">
+        <v>0.853</v>
+      </c>
+      <c r="L44">
+        <v>5.957</v>
+      </c>
+      <c r="M44">
+        <v>0.10345566</v>
+      </c>
+      <c r="N44">
+        <v>5.85354434</v>
+      </c>
+      <c r="O44">
+        <v>0.8780316510000001</v>
+      </c>
+      <c r="P44">
+        <v>4.975512689</v>
+      </c>
+      <c r="Q44">
+        <v>5.828512689</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3235827396772715</v>
+      </c>
+      <c r="T44">
+        <v>1.510255648624478</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.038845</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>57.58022325699724</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2037289196067137</v>
+      </c>
+      <c r="C45">
+        <v>3.180076616935</v>
+      </c>
+      <c r="D45">
+        <v>5.497776616935</v>
+      </c>
+      <c r="E45">
+        <v>2.3177</v>
+      </c>
+      <c r="F45">
+        <v>2.3177</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>5.39</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.81</v>
+      </c>
+      <c r="K45">
+        <v>0.853</v>
+      </c>
+      <c r="L45">
+        <v>5.957</v>
+      </c>
+      <c r="M45">
+        <v>0.10591889</v>
+      </c>
+      <c r="N45">
+        <v>5.85108111</v>
+      </c>
+      <c r="O45">
+        <v>0.8776621665000002</v>
+      </c>
+      <c r="P45">
+        <v>4.9734189435</v>
+      </c>
+      <c r="Q45">
+        <v>5.826418943499999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3281150343977434</v>
+      </c>
+      <c r="T45">
+        <v>1.5342912475185</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.038845</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>56.2411482975322</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.20346495020061</v>
+      </c>
+      <c r="C46">
+        <v>3.128734357061054</v>
+      </c>
+      <c r="D46">
+        <v>5.500334357061054</v>
+      </c>
+      <c r="E46">
+        <v>2.3716</v>
+      </c>
+      <c r="F46">
+        <v>2.3716</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>5.39</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.81</v>
+      </c>
+      <c r="K46">
+        <v>0.853</v>
+      </c>
+      <c r="L46">
+        <v>5.957</v>
+      </c>
+      <c r="M46">
+        <v>0.10838212</v>
+      </c>
+      <c r="N46">
+        <v>5.84861788</v>
+      </c>
+      <c r="O46">
+        <v>0.8772926820000001</v>
+      </c>
+      <c r="P46">
+        <v>4.971325198</v>
+      </c>
+      <c r="Q46">
+        <v>5.824325197999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3328091967868035</v>
+      </c>
+      <c r="T46">
+        <v>1.559185260658737</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.038845</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>54.96294038167918</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2032009807945062</v>
+      </c>
+      <c r="C47">
+        <v>3.077394478178547</v>
+      </c>
+      <c r="D47">
+        <v>5.502894478178547</v>
+      </c>
+      <c r="E47">
+        <v>2.4255</v>
+      </c>
+      <c r="F47">
+        <v>2.4255</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>5.39</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.81</v>
+      </c>
+      <c r="K47">
+        <v>0.853</v>
+      </c>
+      <c r="L47">
+        <v>5.957</v>
+      </c>
+      <c r="M47">
+        <v>0.11084535</v>
+      </c>
+      <c r="N47">
+        <v>5.84615465</v>
+      </c>
+      <c r="O47">
+        <v>0.8769231975000001</v>
+      </c>
+      <c r="P47">
+        <v>4.9692314525</v>
+      </c>
+      <c r="Q47">
+        <v>5.8222314525</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3376740559900112</v>
+      </c>
+      <c r="T47">
+        <v>1.584984510640437</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.038845</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>53.74154170653076</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2029370113884024</v>
+      </c>
+      <c r="C48">
+        <v>3.026056983613712</v>
+      </c>
+      <c r="D48">
+        <v>5.505456983613712</v>
+      </c>
+      <c r="E48">
+        <v>2.4794</v>
+      </c>
+      <c r="F48">
+        <v>2.4794</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>5.39</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.81</v>
+      </c>
+      <c r="K48">
+        <v>0.853</v>
+      </c>
+      <c r="L48">
+        <v>5.957</v>
+      </c>
+      <c r="M48">
+        <v>0.11330858</v>
+      </c>
+      <c r="N48">
+        <v>5.84369142</v>
+      </c>
+      <c r="O48">
+        <v>0.8765537130000001</v>
+      </c>
+      <c r="P48">
+        <v>4.967137707</v>
+      </c>
+      <c r="Q48">
+        <v>5.820137707</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3427190951637082</v>
+      </c>
+      <c r="T48">
+        <v>1.611739288399237</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.038845</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>52.57324732160617</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2026730419822987</v>
+      </c>
+      <c r="C49">
+        <v>2.974721876698984</v>
+      </c>
+      <c r="D49">
+        <v>5.508021876698984</v>
+      </c>
+      <c r="E49">
+        <v>2.5333</v>
+      </c>
+      <c r="F49">
+        <v>2.5333</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>5.39</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.81</v>
+      </c>
+      <c r="K49">
+        <v>0.853</v>
+      </c>
+      <c r="L49">
+        <v>5.957</v>
+      </c>
+      <c r="M49">
+        <v>0.11577181</v>
+      </c>
+      <c r="N49">
+        <v>5.84122819</v>
+      </c>
+      <c r="O49">
+        <v>0.8761842285000001</v>
+      </c>
+      <c r="P49">
+        <v>4.965043961499999</v>
+      </c>
+      <c r="Q49">
+        <v>5.818043961499999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3479545131741484</v>
+      </c>
+      <c r="T49">
+        <v>1.639503680413086</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.038845</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>51.45466759135923</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2024090725761949</v>
+      </c>
+      <c r="C50">
+        <v>2.923389160773004</v>
+      </c>
+      <c r="D50">
+        <v>5.510589160773003</v>
+      </c>
+      <c r="E50">
+        <v>2.5872</v>
+      </c>
+      <c r="F50">
+        <v>2.5872</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>5.39</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.81</v>
+      </c>
+      <c r="K50">
+        <v>0.853</v>
+      </c>
+      <c r="L50">
+        <v>5.957</v>
+      </c>
+      <c r="M50">
+        <v>0.11823504</v>
+      </c>
+      <c r="N50">
+        <v>5.83876496</v>
+      </c>
+      <c r="O50">
+        <v>0.8758147440000001</v>
+      </c>
+      <c r="P50">
+        <v>4.962950215999999</v>
+      </c>
+      <c r="Q50">
+        <v>5.815950215999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3533912934157594</v>
+      </c>
+      <c r="T50">
+        <v>1.668335933658236</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.038845</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>50.38269534987259</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2021451031700911</v>
+      </c>
+      <c r="C51">
+        <v>2.872058839180645</v>
+      </c>
+      <c r="D51">
+        <v>5.513158839180645</v>
+      </c>
+      <c r="E51">
+        <v>2.6411</v>
+      </c>
+      <c r="F51">
+        <v>2.6411</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>5.39</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.81</v>
+      </c>
+      <c r="K51">
+        <v>0.853</v>
+      </c>
+      <c r="L51">
+        <v>5.957</v>
+      </c>
+      <c r="M51">
+        <v>0.12069827</v>
+      </c>
+      <c r="N51">
+        <v>5.83630173</v>
+      </c>
+      <c r="O51">
+        <v>0.8754452595000001</v>
+      </c>
+      <c r="P51">
+        <v>4.9608564705</v>
+      </c>
+      <c r="Q51">
+        <v>5.813856470499999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3590412807256689</v>
+      </c>
+      <c r="T51">
+        <v>1.698298863501236</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.038845</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>49.35447707742621</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2018811337639874</v>
+      </c>
+      <c r="C52">
+        <v>2.820730915273022</v>
+      </c>
+      <c r="D52">
+        <v>5.515730915273022</v>
+      </c>
+      <c r="E52">
+        <v>2.695</v>
+      </c>
+      <c r="F52">
+        <v>2.695</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>5.39</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.81</v>
+      </c>
+      <c r="K52">
+        <v>0.853</v>
+      </c>
+      <c r="L52">
+        <v>5.957</v>
+      </c>
+      <c r="M52">
+        <v>0.1231615</v>
+      </c>
+      <c r="N52">
+        <v>5.8338385</v>
+      </c>
+      <c r="O52">
+        <v>0.8750757750000001</v>
+      </c>
+      <c r="P52">
+        <v>4.958762725</v>
+      </c>
+      <c r="Q52">
+        <v>5.811762724999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3649172675279748</v>
+      </c>
+      <c r="T52">
+        <v>1.729460310537956</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.038845</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>48.36738753587768</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2016171643578836</v>
+      </c>
+      <c r="C53">
+        <v>2.769405392407507</v>
+      </c>
+      <c r="D53">
+        <v>5.518305392407507</v>
+      </c>
+      <c r="E53">
+        <v>2.7489</v>
+      </c>
+      <c r="F53">
+        <v>2.7489</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>5.39</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.81</v>
+      </c>
+      <c r="K53">
+        <v>0.853</v>
+      </c>
+      <c r="L53">
+        <v>5.957</v>
+      </c>
+      <c r="M53">
+        <v>0.12562473</v>
+      </c>
+      <c r="N53">
+        <v>5.83137527</v>
+      </c>
+      <c r="O53">
+        <v>0.8747062905</v>
+      </c>
+      <c r="P53">
+        <v>4.9566689795</v>
+      </c>
+      <c r="Q53">
+        <v>5.8096689795</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3710330905262931</v>
+      </c>
+      <c r="T53">
+        <v>1.761893653372093</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.038845</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>47.41900738811538</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2013531949517799</v>
+      </c>
+      <c r="C54">
+        <v>2.718082273947739</v>
+      </c>
+      <c r="D54">
+        <v>5.520882273947739</v>
+      </c>
+      <c r="E54">
+        <v>2.8028</v>
+      </c>
+      <c r="F54">
+        <v>2.8028</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>5.39</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.81</v>
+      </c>
+      <c r="K54">
+        <v>0.853</v>
+      </c>
+      <c r="L54">
+        <v>5.957</v>
+      </c>
+      <c r="M54">
+        <v>0.12808796</v>
+      </c>
+      <c r="N54">
+        <v>5.82891204</v>
+      </c>
+      <c r="O54">
+        <v>0.8743368060000001</v>
+      </c>
+      <c r="P54">
+        <v>4.954575234</v>
+      </c>
+      <c r="Q54">
+        <v>5.807575234</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3774037394828747</v>
+      </c>
+      <c r="T54">
+        <v>1.795678385490986</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.038845</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>46.50710339988239</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.201089225545676</v>
+      </c>
+      <c r="C55">
+        <v>2.666761563263648</v>
+      </c>
+      <c r="D55">
+        <v>5.523461563263648</v>
+      </c>
+      <c r="E55">
+        <v>2.8567</v>
+      </c>
+      <c r="F55">
+        <v>2.8567</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>5.39</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.81</v>
+      </c>
+      <c r="K55">
+        <v>0.853</v>
+      </c>
+      <c r="L55">
+        <v>5.957</v>
+      </c>
+      <c r="M55">
+        <v>0.13055119</v>
+      </c>
+      <c r="N55">
+        <v>5.82644881</v>
+      </c>
+      <c r="O55">
+        <v>0.8739673215000001</v>
+      </c>
+      <c r="P55">
+        <v>4.952481488499999</v>
+      </c>
+      <c r="Q55">
+        <v>5.805481488499999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3840454798844172</v>
+      </c>
+      <c r="T55">
+        <v>1.830900765785151</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.038845</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>45.62961088290347</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2008252561395723</v>
+      </c>
+      <c r="C56">
+        <v>2.615443263731461</v>
+      </c>
+      <c r="D56">
+        <v>5.526043263731461</v>
+      </c>
+      <c r="E56">
+        <v>2.9106</v>
+      </c>
+      <c r="F56">
+        <v>2.9106</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>5.39</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.81</v>
+      </c>
+      <c r="K56">
+        <v>0.853</v>
+      </c>
+      <c r="L56">
+        <v>5.957</v>
+      </c>
+      <c r="M56">
+        <v>0.13301442</v>
+      </c>
+      <c r="N56">
+        <v>5.82398558</v>
+      </c>
+      <c r="O56">
+        <v>0.873597837</v>
+      </c>
+      <c r="P56">
+        <v>4.950387742999999</v>
+      </c>
+      <c r="Q56">
+        <v>5.803387742999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3909759916077659</v>
+      </c>
+      <c r="T56">
+        <v>1.867654553918193</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.038845</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>44.78461808877563</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2005612867334686</v>
+      </c>
+      <c r="C57">
+        <v>2.564127378733722</v>
+      </c>
+      <c r="D57">
+        <v>5.528627378733722</v>
+      </c>
+      <c r="E57">
+        <v>2.9645</v>
+      </c>
+      <c r="F57">
+        <v>2.9645</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>5.39</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.81</v>
+      </c>
+      <c r="K57">
+        <v>0.853</v>
+      </c>
+      <c r="L57">
+        <v>5.957</v>
+      </c>
+      <c r="M57">
+        <v>0.13547765</v>
+      </c>
+      <c r="N57">
+        <v>5.82152235</v>
+      </c>
+      <c r="O57">
+        <v>0.8732283525000001</v>
+      </c>
+      <c r="P57">
+        <v>4.9482939975</v>
+      </c>
+      <c r="Q57">
+        <v>5.801293997499999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3982145260743746</v>
+      </c>
+      <c r="T57">
+        <v>1.906041843746036</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.15</v>
+      </c>
+      <c r="W57">
+        <v>0.038845</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>43.97035230534334</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2002973173273648</v>
+      </c>
+      <c r="C58">
+        <v>2.512813911659304</v>
+      </c>
+      <c r="D58">
+        <v>5.531213911659305</v>
+      </c>
+      <c r="E58">
+        <v>3.0184</v>
+      </c>
+      <c r="F58">
+        <v>3.0184</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>5.39</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.81</v>
+      </c>
+      <c r="K58">
+        <v>0.853</v>
+      </c>
+      <c r="L58">
+        <v>5.957</v>
+      </c>
+      <c r="M58">
+        <v>0.13794088</v>
+      </c>
+      <c r="N58">
+        <v>5.819059119999999</v>
+      </c>
+      <c r="O58">
+        <v>0.872858868</v>
+      </c>
+      <c r="P58">
+        <v>4.946200252</v>
+      </c>
+      <c r="Q58">
+        <v>5.799200251999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.40578208483492</v>
+      </c>
+      <c r="T58">
+        <v>1.946174010384236</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.15</v>
+      </c>
+      <c r="W58">
+        <v>0.038845</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>43.18516744274793</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.200033347921261</v>
+      </c>
+      <c r="C59">
+        <v>2.461502865903426</v>
+      </c>
+      <c r="D59">
+        <v>5.533802865903426</v>
+      </c>
+      <c r="E59">
+        <v>3.0723</v>
+      </c>
+      <c r="F59">
+        <v>3.0723</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>5.39</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.81</v>
+      </c>
+      <c r="K59">
+        <v>0.853</v>
+      </c>
+      <c r="L59">
+        <v>5.957</v>
+      </c>
+      <c r="M59">
+        <v>0.14040411</v>
+      </c>
+      <c r="N59">
+        <v>5.816595889999999</v>
+      </c>
+      <c r="O59">
+        <v>0.8724893835</v>
+      </c>
+      <c r="P59">
+        <v>4.944106506499999</v>
+      </c>
+      <c r="Q59">
+        <v>5.797106506499999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4137016230727001</v>
+      </c>
+      <c r="T59">
+        <v>1.988172789424213</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.15</v>
+      </c>
+      <c r="W59">
+        <v>0.038845</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>42.42753292620849</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1997693785151573</v>
+      </c>
+      <c r="C60">
+        <v>2.410194244867666</v>
+      </c>
+      <c r="D60">
+        <v>5.536394244867665</v>
+      </c>
+      <c r="E60">
+        <v>3.126199999999999</v>
+      </c>
+      <c r="F60">
+        <v>3.126199999999999</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>5.39</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.81</v>
+      </c>
+      <c r="K60">
+        <v>0.853</v>
+      </c>
+      <c r="L60">
+        <v>5.957</v>
+      </c>
+      <c r="M60">
+        <v>0.14286734</v>
+      </c>
+      <c r="N60">
+        <v>5.81413266</v>
+      </c>
+      <c r="O60">
+        <v>0.8721198990000002</v>
+      </c>
+      <c r="P60">
+        <v>4.942012761</v>
+      </c>
+      <c r="Q60">
+        <v>5.795012761</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4219982821789459</v>
+      </c>
+      <c r="T60">
+        <v>2.032171510323236</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.15</v>
+      </c>
+      <c r="W60">
+        <v>0.038845</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>41.6960237378256</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1995054091090535</v>
+      </c>
+      <c r="C61">
+        <v>2.358888051959975</v>
+      </c>
+      <c r="D61">
+        <v>5.538988051959975</v>
+      </c>
+      <c r="E61">
+        <v>3.180099999999999</v>
+      </c>
+      <c r="F61">
+        <v>3.180099999999999</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>5.39</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.81</v>
+      </c>
+      <c r="K61">
+        <v>0.853</v>
+      </c>
+      <c r="L61">
+        <v>5.957</v>
+      </c>
+      <c r="M61">
+        <v>0.14533057</v>
+      </c>
+      <c r="N61">
+        <v>5.81166943</v>
+      </c>
+      <c r="O61">
+        <v>0.8717504145000001</v>
+      </c>
+      <c r="P61">
+        <v>4.9399190155</v>
+      </c>
+      <c r="Q61">
+        <v>5.7929190155</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4306996563635451</v>
+      </c>
+      <c r="T61">
+        <v>2.078316510290504</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.15</v>
+      </c>
+      <c r="W61">
+        <v>0.038845</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>40.98931147108279</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1992414397029497</v>
+      </c>
+      <c r="C62">
+        <v>2.307584290594697</v>
+      </c>
+      <c r="D62">
+        <v>5.541584290594696</v>
+      </c>
+      <c r="E62">
+        <v>3.234</v>
+      </c>
+      <c r="F62">
+        <v>3.234</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>5.39</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.81</v>
+      </c>
+      <c r="K62">
+        <v>0.853</v>
+      </c>
+      <c r="L62">
+        <v>5.957</v>
+      </c>
+      <c r="M62">
+        <v>0.1477938</v>
+      </c>
+      <c r="N62">
+        <v>5.8092062</v>
+      </c>
+      <c r="O62">
+        <v>0.8713809300000002</v>
+      </c>
+      <c r="P62">
+        <v>4.93782527</v>
+      </c>
+      <c r="Q62">
+        <v>5.79082527</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4398360992573743</v>
+      </c>
+      <c r="T62">
+        <v>2.126768760256135</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.15</v>
+      </c>
+      <c r="W62">
+        <v>0.038845</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>40.30615627989808</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.198977470296846</v>
+      </c>
+      <c r="C63">
+        <v>2.256282964192576</v>
+      </c>
+      <c r="D63">
+        <v>5.544182964192576</v>
+      </c>
+      <c r="E63">
+        <v>3.2879</v>
+      </c>
+      <c r="F63">
+        <v>3.2879</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>5.39</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.81</v>
+      </c>
+      <c r="K63">
+        <v>0.853</v>
+      </c>
+      <c r="L63">
+        <v>5.957</v>
+      </c>
+      <c r="M63">
+        <v>0.15025703</v>
+      </c>
+      <c r="N63">
+        <v>5.80674297</v>
+      </c>
+      <c r="O63">
+        <v>0.8710114455000002</v>
+      </c>
+      <c r="P63">
+        <v>4.9357315245</v>
+      </c>
+      <c r="Q63">
+        <v>5.788731524499999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4494410776842204</v>
+      </c>
+      <c r="T63">
+        <v>2.177705740989235</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.15</v>
+      </c>
+      <c r="W63">
+        <v>0.038845</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>39.64539961957188</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1987135008907422</v>
+      </c>
+      <c r="C64">
+        <v>2.204984076180779</v>
+      </c>
+      <c r="D64">
+        <v>5.546784076180779</v>
+      </c>
+      <c r="E64">
+        <v>3.3418</v>
+      </c>
+      <c r="F64">
+        <v>3.3418</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>5.39</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.81</v>
+      </c>
+      <c r="K64">
+        <v>0.853</v>
+      </c>
+      <c r="L64">
+        <v>5.957</v>
+      </c>
+      <c r="M64">
+        <v>0.15272026</v>
+      </c>
+      <c r="N64">
+        <v>5.80427974</v>
+      </c>
+      <c r="O64">
+        <v>0.8706419610000001</v>
+      </c>
+      <c r="P64">
+        <v>4.933637779</v>
+      </c>
+      <c r="Q64">
+        <v>5.786637778999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4595515812914269</v>
+      </c>
+      <c r="T64">
+        <v>2.23132361544513</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.15</v>
+      </c>
+      <c r="W64">
+        <v>0.038845</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>39.00595769022394</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1984495314846385</v>
+      </c>
+      <c r="C65">
+        <v>2.153687629992909</v>
+      </c>
+      <c r="D65">
+        <v>5.549387629992909</v>
+      </c>
+      <c r="E65">
+        <v>3.3957</v>
+      </c>
+      <c r="F65">
+        <v>3.3957</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>5.39</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.81</v>
+      </c>
+      <c r="K65">
+        <v>0.853</v>
+      </c>
+      <c r="L65">
+        <v>5.957</v>
+      </c>
+      <c r="M65">
+        <v>0.15518349</v>
+      </c>
+      <c r="N65">
+        <v>5.80181651</v>
+      </c>
+      <c r="O65">
+        <v>0.8702724765000002</v>
+      </c>
+      <c r="P65">
+        <v>4.9315440335</v>
+      </c>
+      <c r="Q65">
+        <v>5.7845440335</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4702085986071309</v>
+      </c>
+      <c r="T65">
+        <v>2.287839753385127</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.15</v>
+      </c>
+      <c r="W65">
+        <v>0.038845</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>38.38681550466483</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1981855620785347</v>
+      </c>
+      <c r="C66">
+        <v>2.102393629069015</v>
+      </c>
+      <c r="D66">
+        <v>5.551993629069015</v>
+      </c>
+      <c r="E66">
+        <v>3.4496</v>
+      </c>
+      <c r="F66">
+        <v>3.4496</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>5.39</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.81</v>
+      </c>
+      <c r="K66">
+        <v>0.853</v>
+      </c>
+      <c r="L66">
+        <v>5.957</v>
+      </c>
+      <c r="M66">
+        <v>0.15764672</v>
+      </c>
+      <c r="N66">
+        <v>5.79935328</v>
+      </c>
+      <c r="O66">
+        <v>0.8699029920000001</v>
+      </c>
+      <c r="P66">
+        <v>4.929450288</v>
+      </c>
+      <c r="Q66">
+        <v>5.782450288</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4814576724403741</v>
+      </c>
+      <c r="T66">
+        <v>2.347495676766235</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.15</v>
+      </c>
+      <c r="W66">
+        <v>0.038845</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>37.78702151240444</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1979215926724309</v>
+      </c>
+      <c r="C67">
+        <v>2.05110207685561</v>
+      </c>
+      <c r="D67">
+        <v>5.55460207685561</v>
+      </c>
+      <c r="E67">
+        <v>3.5035</v>
+      </c>
+      <c r="F67">
+        <v>3.5035</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>5.39</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.81</v>
+      </c>
+      <c r="K67">
+        <v>0.853</v>
+      </c>
+      <c r="L67">
+        <v>5.957</v>
+      </c>
+      <c r="M67">
+        <v>0.16010995</v>
+      </c>
+      <c r="N67">
+        <v>5.79689005</v>
+      </c>
+      <c r="O67">
+        <v>0.8695335075000001</v>
+      </c>
+      <c r="P67">
+        <v>4.9273565425</v>
+      </c>
+      <c r="Q67">
+        <v>5.7803565425</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4933495504926598</v>
+      </c>
+      <c r="T67">
+        <v>2.410560510054835</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.038845</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>37.20568271990592</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1976576232663272</v>
+      </c>
+      <c r="C68">
+        <v>1.999812976805692</v>
+      </c>
+      <c r="D68">
+        <v>5.557212976805692</v>
+      </c>
+      <c r="E68">
+        <v>3.5574</v>
+      </c>
+      <c r="F68">
+        <v>3.5574</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>5.39</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.81</v>
+      </c>
+      <c r="K68">
+        <v>0.853</v>
+      </c>
+      <c r="L68">
+        <v>5.957</v>
+      </c>
+      <c r="M68">
+        <v>0.16257318</v>
+      </c>
+      <c r="N68">
+        <v>5.79442682</v>
+      </c>
+      <c r="O68">
+        <v>0.8691640230000002</v>
+      </c>
+      <c r="P68">
+        <v>4.925262797</v>
+      </c>
+      <c r="Q68">
+        <v>5.778262797</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5059409507833152</v>
+      </c>
+      <c r="T68">
+        <v>2.477335039419235</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.15</v>
+      </c>
+      <c r="W68">
+        <v>0.038845</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>36.64196025445279</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1973936538602234</v>
+      </c>
+      <c r="C69">
+        <v>1.94852633237875</v>
+      </c>
+      <c r="D69">
+        <v>5.55982633237875</v>
+      </c>
+      <c r="E69">
+        <v>3.6113</v>
+      </c>
+      <c r="F69">
+        <v>3.6113</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>5.39</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.81</v>
+      </c>
+      <c r="K69">
+        <v>0.853</v>
+      </c>
+      <c r="L69">
+        <v>5.957</v>
+      </c>
+      <c r="M69">
+        <v>0.16503641</v>
+      </c>
+      <c r="N69">
+        <v>5.79196359</v>
+      </c>
+      <c r="O69">
+        <v>0.8687945385000001</v>
+      </c>
+      <c r="P69">
+        <v>4.9231690515</v>
+      </c>
+      <c r="Q69">
+        <v>5.776169051499999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5192954662431013</v>
+      </c>
+      <c r="T69">
+        <v>2.548156509957235</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.15</v>
+      </c>
+      <c r="W69">
+        <v>0.038845</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>36.09506532528185</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1971296844541196</v>
+      </c>
+      <c r="C70">
+        <v>1.897242147040787</v>
+      </c>
+      <c r="D70">
+        <v>5.562442147040787</v>
+      </c>
+      <c r="E70">
+        <v>3.6652</v>
+      </c>
+      <c r="F70">
+        <v>3.6652</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>5.39</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.81</v>
+      </c>
+      <c r="K70">
+        <v>0.853</v>
+      </c>
+      <c r="L70">
+        <v>5.957</v>
+      </c>
+      <c r="M70">
+        <v>0.16749964</v>
+      </c>
+      <c r="N70">
+        <v>5.78950036</v>
+      </c>
+      <c r="O70">
+        <v>0.8684250540000001</v>
+      </c>
+      <c r="P70">
+        <v>4.921075306</v>
+      </c>
+      <c r="Q70">
+        <v>5.774075305999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5334846389191239</v>
+      </c>
+      <c r="T70">
+        <v>2.62340432240386</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.15</v>
+      </c>
+      <c r="W70">
+        <v>0.038845</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>35.56425554108653</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1968657150480159</v>
+      </c>
+      <c r="C71">
+        <v>1.845960424264326</v>
+      </c>
+      <c r="D71">
+        <v>5.565060424264326</v>
+      </c>
+      <c r="E71">
+        <v>3.7191</v>
+      </c>
+      <c r="F71">
+        <v>3.7191</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>5.39</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.81</v>
+      </c>
+      <c r="K71">
+        <v>0.853</v>
+      </c>
+      <c r="L71">
+        <v>5.957</v>
+      </c>
+      <c r="M71">
+        <v>0.16996287</v>
+      </c>
+      <c r="N71">
+        <v>5.78703713</v>
+      </c>
+      <c r="O71">
+        <v>0.8680555695000001</v>
+      </c>
+      <c r="P71">
+        <v>4.9189815605</v>
+      </c>
+      <c r="Q71">
+        <v>5.7719815605</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.548589242090374</v>
+      </c>
+      <c r="T71">
+        <v>2.703506832427687</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.15</v>
+      </c>
+      <c r="W71">
+        <v>0.038845</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>35.04883154773745</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1966017456419121</v>
+      </c>
+      <c r="C72">
+        <v>1.794681167528438</v>
+      </c>
+      <c r="D72">
+        <v>5.567681167528439</v>
+      </c>
+      <c r="E72">
+        <v>3.773</v>
+      </c>
+      <c r="F72">
+        <v>3.773</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>5.39</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.81</v>
+      </c>
+      <c r="K72">
+        <v>0.853</v>
+      </c>
+      <c r="L72">
+        <v>5.957</v>
+      </c>
+      <c r="M72">
+        <v>0.1724261</v>
+      </c>
+      <c r="N72">
+        <v>5.7845739</v>
+      </c>
+      <c r="O72">
+        <v>0.8676860850000001</v>
+      </c>
+      <c r="P72">
+        <v>4.916887815</v>
+      </c>
+      <c r="Q72">
+        <v>5.769887815</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5647008188063738</v>
+      </c>
+      <c r="T72">
+        <v>2.788949509786435</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.15</v>
+      </c>
+      <c r="W72">
+        <v>0.038845</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>34.54813395419834</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1963377762358084</v>
+      </c>
+      <c r="C73">
+        <v>1.743404380318748</v>
+      </c>
+      <c r="D73">
+        <v>5.570304380318747</v>
+      </c>
+      <c r="E73">
+        <v>3.8269</v>
+      </c>
+      <c r="F73">
+        <v>3.8269</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>5.39</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.81</v>
+      </c>
+      <c r="K73">
+        <v>0.853</v>
+      </c>
+      <c r="L73">
+        <v>5.957</v>
+      </c>
+      <c r="M73">
+        <v>0.17488933</v>
+      </c>
+      <c r="N73">
+        <v>5.78211067</v>
+      </c>
+      <c r="O73">
+        <v>0.8673166005000001</v>
+      </c>
+      <c r="P73">
+        <v>4.914794069499999</v>
+      </c>
+      <c r="Q73">
+        <v>5.767794069499999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5819235387441668</v>
+      </c>
+      <c r="T73">
+        <v>2.880284785583717</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.15</v>
+      </c>
+      <c r="W73">
+        <v>0.038845</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>34.06154051822372</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1960738068297046</v>
+      </c>
+      <c r="C74">
+        <v>1.692130066127452</v>
+      </c>
+      <c r="D74">
+        <v>5.572930066127451</v>
+      </c>
+      <c r="E74">
+        <v>3.8808</v>
+      </c>
+      <c r="F74">
+        <v>3.8808</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>5.39</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.81</v>
+      </c>
+      <c r="K74">
+        <v>0.853</v>
+      </c>
+      <c r="L74">
+        <v>5.957</v>
+      </c>
+      <c r="M74">
+        <v>0.17735256</v>
+      </c>
+      <c r="N74">
+        <v>5.77964744</v>
+      </c>
+      <c r="O74">
+        <v>0.8669471160000001</v>
+      </c>
+      <c r="P74">
+        <v>4.912700323999999</v>
+      </c>
+      <c r="Q74">
+        <v>5.765700323999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6003764529632305</v>
+      </c>
+      <c r="T74">
+        <v>2.978144009652234</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.15</v>
+      </c>
+      <c r="W74">
+        <v>0.038845</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>33.58846356658172</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1958098374236008</v>
+      </c>
+      <c r="C75">
+        <v>1.640858228453335</v>
+      </c>
+      <c r="D75">
+        <v>5.575558228453334</v>
+      </c>
+      <c r="E75">
+        <v>3.9347</v>
+      </c>
+      <c r="F75">
+        <v>3.9347</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>5.39</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.81</v>
+      </c>
+      <c r="K75">
+        <v>0.853</v>
+      </c>
+      <c r="L75">
+        <v>5.957</v>
+      </c>
+      <c r="M75">
+        <v>0.17981579</v>
+      </c>
+      <c r="N75">
+        <v>5.77718421</v>
+      </c>
+      <c r="O75">
+        <v>0.8665776315000001</v>
+      </c>
+      <c r="P75">
+        <v>4.910606578499999</v>
+      </c>
+      <c r="Q75">
+        <v>5.763606578499999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6201962497170399</v>
+      </c>
+      <c r="T75">
+        <v>3.083252065133233</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.15</v>
+      </c>
+      <c r="W75">
+        <v>0.038845</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>33.12834762731348</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.195545868017497</v>
+      </c>
+      <c r="C76">
+        <v>1.589588870801783</v>
+      </c>
+      <c r="D76">
+        <v>5.578188870801783</v>
+      </c>
+      <c r="E76">
+        <v>3.9886</v>
+      </c>
+      <c r="F76">
+        <v>3.9886</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>5.39</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.81</v>
+      </c>
+      <c r="K76">
+        <v>0.853</v>
+      </c>
+      <c r="L76">
+        <v>5.957</v>
+      </c>
+      <c r="M76">
+        <v>0.18227902</v>
+      </c>
+      <c r="N76">
+        <v>5.77472098</v>
+      </c>
+      <c r="O76">
+        <v>0.866208147</v>
+      </c>
+      <c r="P76">
+        <v>4.908512833</v>
+      </c>
+      <c r="Q76">
+        <v>5.761512832999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6415406462211424</v>
+      </c>
+      <c r="T76">
+        <v>3.196445355651233</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.15</v>
+      </c>
+      <c r="W76">
+        <v>0.038845</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>32.68066725397141</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1952818986113933</v>
+      </c>
+      <c r="C77">
+        <v>1.538321996684804</v>
+      </c>
+      <c r="D77">
+        <v>5.580821996684803</v>
+      </c>
+      <c r="E77">
+        <v>4.0425</v>
+      </c>
+      <c r="F77">
+        <v>4.0425</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>5.39</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.81</v>
+      </c>
+      <c r="K77">
+        <v>0.853</v>
+      </c>
+      <c r="L77">
+        <v>5.957</v>
+      </c>
+      <c r="M77">
+        <v>0.18474225</v>
+      </c>
+      <c r="N77">
+        <v>5.77225775</v>
+      </c>
+      <c r="O77">
+        <v>0.8658386625000001</v>
+      </c>
+      <c r="P77">
+        <v>4.9064190875</v>
+      </c>
+      <c r="Q77">
+        <v>5.7594190875</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.6645925944455733</v>
+      </c>
+      <c r="T77">
+        <v>3.318694109410673</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.15</v>
+      </c>
+      <c r="W77">
+        <v>0.038845</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>32.24492502391846</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1950179292052895</v>
+      </c>
+      <c r="C78">
+        <v>1.487057609621038</v>
+      </c>
+      <c r="D78">
+        <v>5.583457609621038</v>
+      </c>
+      <c r="E78">
+        <v>4.0964</v>
+      </c>
+      <c r="F78">
+        <v>4.0964</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>5.39</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.81</v>
+      </c>
+      <c r="K78">
+        <v>0.853</v>
+      </c>
+      <c r="L78">
+        <v>5.957</v>
+      </c>
+      <c r="M78">
+        <v>0.18720548</v>
+      </c>
+      <c r="N78">
+        <v>5.76979452</v>
+      </c>
+      <c r="O78">
+        <v>0.8654691780000001</v>
+      </c>
+      <c r="P78">
+        <v>4.904325342</v>
+      </c>
+      <c r="Q78">
+        <v>5.757325342</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6895655383553732</v>
+      </c>
+      <c r="T78">
+        <v>3.451130259316733</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.15</v>
+      </c>
+      <c r="W78">
+        <v>0.038845</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>31.82064969465637</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1947539597991857</v>
+      </c>
+      <c r="C79">
+        <v>1.435795713135778</v>
+      </c>
+      <c r="D79">
+        <v>5.586095713135777</v>
+      </c>
+      <c r="E79">
+        <v>4.1503</v>
+      </c>
+      <c r="F79">
+        <v>4.1503</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>5.39</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.81</v>
+      </c>
+      <c r="K79">
+        <v>0.853</v>
+      </c>
+      <c r="L79">
+        <v>5.957</v>
+      </c>
+      <c r="M79">
+        <v>0.18966871</v>
+      </c>
+      <c r="N79">
+        <v>5.76733129</v>
+      </c>
+      <c r="O79">
+        <v>0.8650996935</v>
+      </c>
+      <c r="P79">
+        <v>4.902231596499999</v>
+      </c>
+      <c r="Q79">
+        <v>5.755231596499999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7167100426051554</v>
+      </c>
+      <c r="T79">
+        <v>3.595082596171145</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.15</v>
+      </c>
+      <c r="W79">
+        <v>0.038845</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>31.40739450381668</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.194489990393082</v>
+      </c>
+      <c r="C80">
+        <v>1.384536310760977</v>
+      </c>
+      <c r="D80">
+        <v>5.588736310760977</v>
+      </c>
+      <c r="E80">
+        <v>4.2042</v>
+      </c>
+      <c r="F80">
+        <v>4.2042</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>5.39</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.81</v>
+      </c>
+      <c r="K80">
+        <v>0.853</v>
+      </c>
+      <c r="L80">
+        <v>5.957</v>
+      </c>
+      <c r="M80">
+        <v>0.19213194</v>
+      </c>
+      <c r="N80">
+        <v>5.76486806</v>
+      </c>
+      <c r="O80">
+        <v>0.8647302090000001</v>
+      </c>
+      <c r="P80">
+        <v>4.900137850999999</v>
+      </c>
+      <c r="Q80">
+        <v>5.753137850999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.7463222290594635</v>
+      </c>
+      <c r="T80">
+        <v>3.752121509103232</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.15</v>
+      </c>
+      <c r="W80">
+        <v>0.038845</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>31.00473559992159</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1942260209869782</v>
+      </c>
+      <c r="C81">
+        <v>1.333279406035276</v>
+      </c>
+      <c r="D81">
+        <v>5.591379406035276</v>
+      </c>
+      <c r="E81">
+        <v>4.2581</v>
+      </c>
+      <c r="F81">
+        <v>4.2581</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>5.39</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.81</v>
+      </c>
+      <c r="K81">
+        <v>0.853</v>
+      </c>
+      <c r="L81">
+        <v>5.957</v>
+      </c>
+      <c r="M81">
+        <v>0.19459517</v>
+      </c>
+      <c r="N81">
+        <v>5.762404829999999</v>
+      </c>
+      <c r="O81">
+        <v>0.8643607245</v>
+      </c>
+      <c r="P81">
+        <v>4.898044105499999</v>
+      </c>
+      <c r="Q81">
+        <v>5.751044105499999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.7787546237475154</v>
+      </c>
+      <c r="T81">
+        <v>3.924116508981232</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.15</v>
+      </c>
+      <c r="W81">
+        <v>0.038845</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>30.61227059232765</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1939620515808745</v>
+      </c>
+      <c r="C82">
+        <v>1.282025002504007</v>
+      </c>
+      <c r="D82">
+        <v>5.594025002504007</v>
+      </c>
+      <c r="E82">
+        <v>4.312</v>
+      </c>
+      <c r="F82">
+        <v>4.312</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>5.39</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.81</v>
+      </c>
+      <c r="K82">
+        <v>0.853</v>
+      </c>
+      <c r="L82">
+        <v>5.957</v>
+      </c>
+      <c r="M82">
+        <v>0.1970584</v>
+      </c>
+      <c r="N82">
+        <v>5.759941599999999</v>
+      </c>
+      <c r="O82">
+        <v>0.86399124</v>
+      </c>
+      <c r="P82">
+        <v>4.89595036</v>
+      </c>
+      <c r="Q82">
+        <v>5.748950359999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.8144302579043725</v>
+      </c>
+      <c r="T82">
+        <v>4.113311008847032</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.15</v>
+      </c>
+      <c r="W82">
+        <v>0.038845</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>30.22961720992355</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1936980821747707</v>
+      </c>
+      <c r="C83">
+        <v>1.230773103719221</v>
+      </c>
+      <c r="D83">
+        <v>5.596673103719221</v>
+      </c>
+      <c r="E83">
+        <v>4.3659</v>
+      </c>
+      <c r="F83">
+        <v>4.3659</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>5.39</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.81</v>
+      </c>
+      <c r="K83">
+        <v>0.853</v>
+      </c>
+      <c r="L83">
+        <v>5.957</v>
+      </c>
+      <c r="M83">
+        <v>0.19952163</v>
+      </c>
+      <c r="N83">
+        <v>5.757478369999999</v>
+      </c>
+      <c r="O83">
+        <v>0.8636217555000001</v>
+      </c>
+      <c r="P83">
+        <v>4.893856614499999</v>
+      </c>
+      <c r="Q83">
+        <v>5.746856614499999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.8538612219724777</v>
+      </c>
+      <c r="T83">
+        <v>4.322420719225022</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.15</v>
+      </c>
+      <c r="W83">
+        <v>0.038845</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>29.85641205918375</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1934341127686669</v>
+      </c>
+      <c r="C84">
+        <v>1.179523713239695</v>
+      </c>
+      <c r="D84">
+        <v>5.599323713239696</v>
+      </c>
+      <c r="E84">
+        <v>4.4198</v>
+      </c>
+      <c r="F84">
+        <v>4.4198</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>5.39</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.81</v>
+      </c>
+      <c r="K84">
+        <v>0.853</v>
+      </c>
+      <c r="L84">
+        <v>5.957</v>
+      </c>
+      <c r="M84">
+        <v>0.20198486</v>
+      </c>
+      <c r="N84">
+        <v>5.755015139999999</v>
+      </c>
+      <c r="O84">
+        <v>0.863252271</v>
+      </c>
+      <c r="P84">
+        <v>4.891762868999999</v>
+      </c>
+      <c r="Q84">
+        <v>5.744762868999999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.897673404270372</v>
+      </c>
+      <c r="T84">
+        <v>4.554764841867232</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0.15</v>
+      </c>
+      <c r="W84">
+        <v>0.038845</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>29.49230947309614</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1931701433625632</v>
+      </c>
+      <c r="C85">
+        <v>1.128276834630952</v>
+      </c>
+      <c r="D85">
+        <v>5.601976834630952</v>
+      </c>
+      <c r="E85">
+        <v>4.4737</v>
+      </c>
+      <c r="F85">
+        <v>4.4737</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>5.39</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.81</v>
+      </c>
+      <c r="K85">
+        <v>0.853</v>
+      </c>
+      <c r="L85">
+        <v>5.957</v>
+      </c>
+      <c r="M85">
+        <v>0.20444809</v>
+      </c>
+      <c r="N85">
+        <v>5.75255191</v>
+      </c>
+      <c r="O85">
+        <v>0.8628827865000002</v>
+      </c>
+      <c r="P85">
+        <v>4.8896691235</v>
+      </c>
+      <c r="Q85">
+        <v>5.7426691235</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.9466399609562544</v>
+      </c>
+      <c r="T85">
+        <v>4.814443567173232</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0.15</v>
+      </c>
+      <c r="W85">
+        <v>0.038845</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>29.13698044329981</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1929061739564594</v>
+      </c>
+      <c r="C86">
+        <v>1.077032471465275</v>
+      </c>
+      <c r="D86">
+        <v>5.604632471465274</v>
+      </c>
+      <c r="E86">
+        <v>4.5276</v>
+      </c>
+      <c r="F86">
+        <v>4.5276</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>5.39</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.81</v>
+      </c>
+      <c r="K86">
+        <v>0.853</v>
+      </c>
+      <c r="L86">
+        <v>5.957</v>
+      </c>
+      <c r="M86">
+        <v>0.20691132</v>
+      </c>
+      <c r="N86">
+        <v>5.75008868</v>
+      </c>
+      <c r="O86">
+        <v>0.8625133020000002</v>
+      </c>
+      <c r="P86">
+        <v>4.887575378</v>
+      </c>
+      <c r="Q86">
+        <v>5.740575378</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.001727337227871</v>
+      </c>
+      <c r="T86">
+        <v>5.106582133142479</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0.15</v>
+      </c>
+      <c r="W86">
+        <v>0.038845</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>28.79011162849863</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1926422045503557</v>
+      </c>
+      <c r="C87">
+        <v>1.025790627321725</v>
+      </c>
+      <c r="D87">
+        <v>5.607290627321724</v>
+      </c>
+      <c r="E87">
+        <v>4.581499999999999</v>
+      </c>
+      <c r="F87">
+        <v>4.581499999999999</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>5.39</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.81</v>
+      </c>
+      <c r="K87">
+        <v>0.853</v>
+      </c>
+      <c r="L87">
+        <v>5.957</v>
+      </c>
+      <c r="M87">
+        <v>0.20937455</v>
+      </c>
+      <c r="N87">
+        <v>5.74762545</v>
+      </c>
+      <c r="O87">
+        <v>0.8621438175000001</v>
+      </c>
+      <c r="P87">
+        <v>4.8854816325</v>
+      </c>
+      <c r="Q87">
+        <v>5.7384816325</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.064159697002371</v>
+      </c>
+      <c r="T87">
+        <v>5.437672507907629</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0.15</v>
+      </c>
+      <c r="W87">
+        <v>0.038845</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>28.45140443286923</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1923782351442519</v>
+      </c>
+      <c r="C88">
+        <v>0.9745513057861555</v>
+      </c>
+      <c r="D88">
+        <v>5.609951305786155</v>
+      </c>
+      <c r="E88">
+        <v>4.6354</v>
+      </c>
+      <c r="F88">
+        <v>4.6354</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>5.39</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.81</v>
+      </c>
+      <c r="K88">
+        <v>0.853</v>
+      </c>
+      <c r="L88">
+        <v>5.957</v>
+      </c>
+      <c r="M88">
+        <v>0.21183778</v>
+      </c>
+      <c r="N88">
+        <v>5.74516222</v>
+      </c>
+      <c r="O88">
+        <v>0.8617743330000002</v>
+      </c>
+      <c r="P88">
+        <v>4.883387887</v>
+      </c>
+      <c r="Q88">
+        <v>5.736387886999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.135510965316085</v>
+      </c>
+      <c r="T88">
+        <v>5.816061507639227</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0.15</v>
+      </c>
+      <c r="W88">
+        <v>0.038845</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>28.1205741487661</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1921142657381481</v>
+      </c>
+      <c r="C89">
+        <v>0.9233145104512293</v>
+      </c>
+      <c r="D89">
+        <v>5.612614510451229</v>
+      </c>
+      <c r="E89">
+        <v>4.689299999999999</v>
+      </c>
+      <c r="F89">
+        <v>4.689299999999999</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>5.39</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.81</v>
+      </c>
+      <c r="K89">
+        <v>0.853</v>
+      </c>
+      <c r="L89">
+        <v>5.957</v>
+      </c>
+      <c r="M89">
+        <v>0.21430101</v>
+      </c>
+      <c r="N89">
+        <v>5.74269899</v>
+      </c>
+      <c r="O89">
+        <v>0.8614048485000001</v>
+      </c>
+      <c r="P89">
+        <v>4.8812941415</v>
+      </c>
+      <c r="Q89">
+        <v>5.734294141499999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.217839351831908</v>
+      </c>
+      <c r="T89">
+        <v>6.252664199637226</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0.15</v>
+      </c>
+      <c r="W89">
+        <v>0.038845</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>27.7973491585504</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1918502963320444</v>
+      </c>
+      <c r="C90">
+        <v>0.8720802449164324</v>
+      </c>
+      <c r="D90">
+        <v>5.615280244916432</v>
+      </c>
+      <c r="E90">
+        <v>4.7432</v>
+      </c>
+      <c r="F90">
+        <v>4.7432</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>5.39</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.81</v>
+      </c>
+      <c r="K90">
+        <v>0.853</v>
+      </c>
+      <c r="L90">
+        <v>5.957</v>
+      </c>
+      <c r="M90">
+        <v>0.21676424</v>
+      </c>
+      <c r="N90">
+        <v>5.74023576</v>
+      </c>
+      <c r="O90">
+        <v>0.8610353640000001</v>
+      </c>
+      <c r="P90">
+        <v>4.879200396</v>
+      </c>
+      <c r="Q90">
+        <v>5.732200396</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.31388913610037</v>
+      </c>
+      <c r="T90">
+        <v>6.762034006968226</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0.15</v>
+      </c>
+      <c r="W90">
+        <v>0.038845</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>27.48147019083959</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1915863269259406</v>
+      </c>
+      <c r="C91">
+        <v>0.8208485127881007</v>
+      </c>
+      <c r="D91">
+        <v>5.6179485127881</v>
+      </c>
+      <c r="E91">
+        <v>4.797099999999999</v>
+      </c>
+      <c r="F91">
+        <v>4.797099999999999</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>5.39</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.81</v>
+      </c>
+      <c r="K91">
+        <v>0.853</v>
+      </c>
+      <c r="L91">
+        <v>5.957</v>
+      </c>
+      <c r="M91">
+        <v>0.21922747</v>
+      </c>
+      <c r="N91">
+        <v>5.73777253</v>
+      </c>
+      <c r="O91">
+        <v>0.8606658795000002</v>
+      </c>
+      <c r="P91">
+        <v>4.8771066505</v>
+      </c>
+      <c r="Q91">
+        <v>5.7301066505</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.427402517508551</v>
+      </c>
+      <c r="T91">
+        <v>7.364016506541225</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0.15</v>
+      </c>
+      <c r="W91">
+        <v>0.038845</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>27.17268962689758</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1913223575198368</v>
+      </c>
+      <c r="C92">
+        <v>0.7696193176794148</v>
+      </c>
+      <c r="D92">
+        <v>5.620619317679415</v>
+      </c>
+      <c r="E92">
+        <v>4.851</v>
+      </c>
+      <c r="F92">
+        <v>4.851</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>5.39</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.81</v>
+      </c>
+      <c r="K92">
+        <v>0.853</v>
+      </c>
+      <c r="L92">
+        <v>5.957</v>
+      </c>
+      <c r="M92">
+        <v>0.2216907</v>
+      </c>
+      <c r="N92">
+        <v>5.7353093</v>
+      </c>
+      <c r="O92">
+        <v>0.8602963950000001</v>
+      </c>
+      <c r="P92">
+        <v>4.875012905</v>
+      </c>
+      <c r="Q92">
+        <v>5.728012905</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.563618575198369</v>
+      </c>
+      <c r="T92">
+        <v>8.086395506028826</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0.15</v>
+      </c>
+      <c r="W92">
+        <v>0.038845</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>26.87077085326538</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.191058388113733</v>
+      </c>
+      <c r="C93">
+        <v>0.7183926632104427</v>
+      </c>
+      <c r="D93">
+        <v>5.623292663210442</v>
+      </c>
+      <c r="E93">
+        <v>4.9049</v>
+      </c>
+      <c r="F93">
+        <v>4.9049</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>5.39</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.81</v>
+      </c>
+      <c r="K93">
+        <v>0.853</v>
+      </c>
+      <c r="L93">
+        <v>5.957</v>
+      </c>
+      <c r="M93">
+        <v>0.22415393</v>
+      </c>
+      <c r="N93">
+        <v>5.73284607</v>
+      </c>
+      <c r="O93">
+        <v>0.8599269105000001</v>
+      </c>
+      <c r="P93">
+        <v>4.872919159499999</v>
+      </c>
+      <c r="Q93">
+        <v>5.725919159499999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.730104867930368</v>
+      </c>
+      <c r="T93">
+        <v>8.969303172069223</v>
+      </c>
+      <c r="U93">
+        <v>0.0457</v>
+      </c>
+      <c r="V93">
+        <v>0.15</v>
+      </c>
+      <c r="W93">
+        <v>0.038845</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>26.57548765707565</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1907944187076293</v>
+      </c>
+      <c r="C94">
+        <v>0.6671685530081328</v>
+      </c>
+      <c r="D94">
+        <v>5.625968553008133</v>
+      </c>
+      <c r="E94">
+        <v>4.9588</v>
+      </c>
+      <c r="F94">
+        <v>4.9588</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>5.39</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.81</v>
+      </c>
+      <c r="K94">
+        <v>0.853</v>
+      </c>
+      <c r="L94">
+        <v>5.957</v>
+      </c>
+      <c r="M94">
+        <v>0.22661716</v>
+      </c>
+      <c r="N94">
+        <v>5.73038284</v>
+      </c>
+      <c r="O94">
+        <v>0.8595574260000001</v>
+      </c>
+      <c r="P94">
+        <v>4.870825414</v>
+      </c>
+      <c r="Q94">
+        <v>5.723825413999999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.938212733845367</v>
+      </c>
+      <c r="T94">
+        <v>10.07293775461972</v>
+      </c>
+      <c r="U94">
+        <v>0.0457</v>
+      </c>
+      <c r="V94">
+        <v>0.15</v>
+      </c>
+      <c r="W94">
+        <v>0.038845</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>26.28662366080309</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1905304493015256</v>
+      </c>
+      <c r="C95">
+        <v>0.6159469907063473</v>
+      </c>
+      <c r="D95">
+        <v>5.628646990706347</v>
+      </c>
+      <c r="E95">
+        <v>5.0127</v>
+      </c>
+      <c r="F95">
+        <v>5.0127</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>5.39</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.81</v>
+      </c>
+      <c r="K95">
+        <v>0.853</v>
+      </c>
+      <c r="L95">
+        <v>5.957</v>
+      </c>
+      <c r="M95">
+        <v>0.22908039</v>
+      </c>
+      <c r="N95">
+        <v>5.72791961</v>
+      </c>
+      <c r="O95">
+        <v>0.8591879415000001</v>
+      </c>
+      <c r="P95">
+        <v>4.8687316685</v>
+      </c>
+      <c r="Q95">
+        <v>5.721731668499999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.205779990021795</v>
+      </c>
+      <c r="T95">
+        <v>11.49189650361322</v>
+      </c>
+      <c r="U95">
+        <v>0.0457</v>
+      </c>
+      <c r="V95">
+        <v>0.15</v>
+      </c>
+      <c r="W95">
+        <v>0.038845</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>26.00397179348262</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1902664798954218</v>
+      </c>
+      <c r="C96">
+        <v>0.564727979945868</v>
+      </c>
+      <c r="D96">
+        <v>5.631327979945868</v>
+      </c>
+      <c r="E96">
+        <v>5.0666</v>
+      </c>
+      <c r="F96">
+        <v>5.0666</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>5.39</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.81</v>
+      </c>
+      <c r="K96">
+        <v>0.853</v>
+      </c>
+      <c r="L96">
+        <v>5.957</v>
+      </c>
+      <c r="M96">
+        <v>0.23154362</v>
+      </c>
+      <c r="N96">
+        <v>5.72545638</v>
+      </c>
+      <c r="O96">
+        <v>0.8588184570000001</v>
+      </c>
+      <c r="P96">
+        <v>4.866637923</v>
+      </c>
+      <c r="Q96">
+        <v>5.719637923</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.562536331590366</v>
+      </c>
+      <c r="T96">
+        <v>13.38384150227122</v>
+      </c>
+      <c r="U96">
+        <v>0.0457</v>
+      </c>
+      <c r="V96">
+        <v>0.15</v>
+      </c>
+      <c r="W96">
+        <v>0.038845</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>25.72733379567962</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.190002510489318</v>
+      </c>
+      <c r="C97">
+        <v>0.513511524374417</v>
+      </c>
+      <c r="D97">
+        <v>5.634011524374417</v>
+      </c>
+      <c r="E97">
+        <v>5.1205</v>
+      </c>
+      <c r="F97">
+        <v>5.1205</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>5.39</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.81</v>
+      </c>
+      <c r="K97">
+        <v>0.853</v>
+      </c>
+      <c r="L97">
+        <v>5.957</v>
+      </c>
+      <c r="M97">
+        <v>0.23400685</v>
+      </c>
+      <c r="N97">
+        <v>5.72299315</v>
+      </c>
+      <c r="O97">
+        <v>0.8584489725000001</v>
+      </c>
+      <c r="P97">
+        <v>4.8645441775</v>
+      </c>
+      <c r="Q97">
+        <v>5.7175441775</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.061995209786365</v>
+      </c>
+      <c r="T97">
+        <v>16.03256450039243</v>
+      </c>
+      <c r="U97">
+        <v>0.0457</v>
+      </c>
+      <c r="V97">
+        <v>0.15</v>
+      </c>
+      <c r="W97">
+        <v>0.038845</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>25.4565197557251</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1897385410832143</v>
+      </c>
+      <c r="C98">
+        <v>0.4622976276466764</v>
+      </c>
+      <c r="D98">
+        <v>5.636697627646676</v>
+      </c>
+      <c r="E98">
+        <v>5.174399999999999</v>
+      </c>
+      <c r="F98">
+        <v>5.174399999999999</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>5.39</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.81</v>
+      </c>
+      <c r="K98">
+        <v>0.853</v>
+      </c>
+      <c r="L98">
+        <v>5.957</v>
+      </c>
+      <c r="M98">
+        <v>0.23647008</v>
+      </c>
+      <c r="N98">
+        <v>5.72052992</v>
+      </c>
+      <c r="O98">
+        <v>0.8580794880000001</v>
+      </c>
+      <c r="P98">
+        <v>4.862450431999999</v>
+      </c>
+      <c r="Q98">
+        <v>5.715450431999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.811183527080353</v>
+      </c>
+      <c r="T98">
+        <v>20.00564899757418</v>
+      </c>
+      <c r="U98">
+        <v>0.0457</v>
+      </c>
+      <c r="V98">
+        <v>0.15</v>
+      </c>
+      <c r="W98">
+        <v>0.038845</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>25.1913476749363</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1894745716771105</v>
+      </c>
+      <c r="C99">
+        <v>0.4110862934242938</v>
+      </c>
+      <c r="D99">
+        <v>5.639386293424294</v>
+      </c>
+      <c r="E99">
+        <v>5.2283</v>
+      </c>
+      <c r="F99">
+        <v>5.2283</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>5.39</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.81</v>
+      </c>
+      <c r="K99">
+        <v>0.853</v>
+      </c>
+      <c r="L99">
+        <v>5.957</v>
+      </c>
+      <c r="M99">
+        <v>0.23893331</v>
+      </c>
+      <c r="N99">
+        <v>5.71806669</v>
+      </c>
+      <c r="O99">
+        <v>0.8577100035</v>
+      </c>
+      <c r="P99">
+        <v>4.860356686499999</v>
+      </c>
+      <c r="Q99">
+        <v>5.713356686499999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.059830722570346</v>
+      </c>
+      <c r="T99">
+        <v>26.62745649287716</v>
+      </c>
+      <c r="U99">
+        <v>0.0457</v>
+      </c>
+      <c r="V99">
+        <v>0.15</v>
+      </c>
+      <c r="W99">
+        <v>0.038845</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>24.93164305973076</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1892106022710067</v>
+      </c>
+      <c r="C100">
+        <v>0.3598775253759161</v>
+      </c>
+      <c r="D100">
+        <v>5.642077525375916</v>
+      </c>
+      <c r="E100">
+        <v>5.2822</v>
+      </c>
+      <c r="F100">
+        <v>5.2822</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>5.39</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.81</v>
+      </c>
+      <c r="K100">
+        <v>0.853</v>
+      </c>
+      <c r="L100">
+        <v>5.957</v>
+      </c>
+      <c r="M100">
+        <v>0.24139654</v>
+      </c>
+      <c r="N100">
+        <v>5.71560346</v>
+      </c>
+      <c r="O100">
+        <v>0.8573405190000001</v>
+      </c>
+      <c r="P100">
+        <v>4.858262941</v>
+      </c>
+      <c r="Q100">
+        <v>5.711262940999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.55712511355033</v>
+      </c>
+      <c r="T100">
+        <v>39.87107148348312</v>
+      </c>
+      <c r="U100">
+        <v>0.0457</v>
+      </c>
+      <c r="V100">
+        <v>0.15</v>
+      </c>
+      <c r="W100">
+        <v>0.038845</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>24.67723853871311</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.188946632864903</v>
+      </c>
+      <c r="C101">
+        <v>0.3086713271771879</v>
+      </c>
+      <c r="D101">
+        <v>5.644771327177188</v>
+      </c>
+      <c r="E101">
+        <v>5.3361</v>
+      </c>
+      <c r="F101">
+        <v>5.3361</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>5.39</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.81</v>
+      </c>
+      <c r="K101">
+        <v>0.853</v>
+      </c>
+      <c r="L101">
+        <v>5.957</v>
+      </c>
+      <c r="M101">
+        <v>0.24385977</v>
+      </c>
+      <c r="N101">
+        <v>5.71314023</v>
+      </c>
+      <c r="O101">
+        <v>0.8569710345000001</v>
+      </c>
+      <c r="P101">
+        <v>4.8561691955</v>
+      </c>
+      <c r="Q101">
+        <v>5.709169195499999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>15.04900828649028</v>
+      </c>
+      <c r="T101">
+        <v>79.60191645530101</v>
+      </c>
+      <c r="U101">
+        <v>0.0457</v>
+      </c>
+      <c r="V101">
+        <v>0.15</v>
+      </c>
+      <c r="W101">
+        <v>0.038845</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>24.42797350296852</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
